--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="585">
   <si>
     <t>date</t>
   </si>
@@ -1766,6 +1766,9 @@
   </si>
   <si>
     <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
   </si>
 </sst>
 </file>
@@ -2108,7 +2111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE554"/>
+  <dimension ref="A1:AE555"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -54480,6 +54483,101 @@
         <v>10033</v>
       </c>
     </row>
+    <row r="555" spans="1:31">
+      <c r="A555" t="s">
+        <v>584</v>
+      </c>
+      <c r="B555">
+        <v>431</v>
+      </c>
+      <c r="C555">
+        <v>1769</v>
+      </c>
+      <c r="D555">
+        <v>10052</v>
+      </c>
+      <c r="E555">
+        <v>1664</v>
+      </c>
+      <c r="F555">
+        <v>4442</v>
+      </c>
+      <c r="G555">
+        <v>5306</v>
+      </c>
+      <c r="H555">
+        <v>165</v>
+      </c>
+      <c r="I555">
+        <v>10036</v>
+      </c>
+      <c r="J555">
+        <v>7301</v>
+      </c>
+      <c r="K555">
+        <v>3108</v>
+      </c>
+      <c r="L555">
+        <v>876</v>
+      </c>
+      <c r="M555">
+        <v>1254</v>
+      </c>
+      <c r="N555">
+        <v>0</v>
+      </c>
+      <c r="O555">
+        <v>0</v>
+      </c>
+      <c r="P555">
+        <v>2728</v>
+      </c>
+      <c r="Q555">
+        <v>4350</v>
+      </c>
+      <c r="R555">
+        <v>245</v>
+      </c>
+      <c r="S555">
+        <v>2322</v>
+      </c>
+      <c r="T555">
+        <v>244</v>
+      </c>
+      <c r="U555">
+        <v>612</v>
+      </c>
+      <c r="V555">
+        <v>145</v>
+      </c>
+      <c r="W555">
+        <v>943</v>
+      </c>
+      <c r="X555">
+        <v>1313</v>
+      </c>
+      <c r="Y555">
+        <v>57</v>
+      </c>
+      <c r="Z555">
+        <v>260</v>
+      </c>
+      <c r="AA555">
+        <v>2639</v>
+      </c>
+      <c r="AB555">
+        <v>1452</v>
+      </c>
+      <c r="AC555">
+        <v>10044</v>
+      </c>
+      <c r="AD555">
+        <v>4890</v>
+      </c>
+      <c r="AE555">
+        <v>10033</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="586">
   <si>
     <t>date</t>
   </si>
@@ -1769,6 +1769,9 @@
   </si>
   <si>
     <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
   </si>
 </sst>
 </file>
@@ -2111,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE555"/>
+  <dimension ref="A1:AE556"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -54578,6 +54581,101 @@
         <v>10033</v>
       </c>
     </row>
+    <row r="556" spans="1:31">
+      <c r="A556" t="s">
+        <v>585</v>
+      </c>
+      <c r="B556">
+        <v>430</v>
+      </c>
+      <c r="C556">
+        <v>1769</v>
+      </c>
+      <c r="D556">
+        <v>10038</v>
+      </c>
+      <c r="E556">
+        <v>1664</v>
+      </c>
+      <c r="F556">
+        <v>4441</v>
+      </c>
+      <c r="G556">
+        <v>5305</v>
+      </c>
+      <c r="H556">
+        <v>165</v>
+      </c>
+      <c r="I556">
+        <v>10033</v>
+      </c>
+      <c r="J556">
+        <v>7302</v>
+      </c>
+      <c r="K556">
+        <v>3109</v>
+      </c>
+      <c r="L556">
+        <v>879</v>
+      </c>
+      <c r="M556">
+        <v>1255</v>
+      </c>
+      <c r="N556">
+        <v>0</v>
+      </c>
+      <c r="O556">
+        <v>0</v>
+      </c>
+      <c r="P556">
+        <v>2728</v>
+      </c>
+      <c r="Q556">
+        <v>4348</v>
+      </c>
+      <c r="R556">
+        <v>245</v>
+      </c>
+      <c r="S556">
+        <v>2322</v>
+      </c>
+      <c r="T556">
+        <v>244</v>
+      </c>
+      <c r="U556">
+        <v>612</v>
+      </c>
+      <c r="V556">
+        <v>145</v>
+      </c>
+      <c r="W556">
+        <v>943</v>
+      </c>
+      <c r="X556">
+        <v>1313</v>
+      </c>
+      <c r="Y556">
+        <v>57</v>
+      </c>
+      <c r="Z556">
+        <v>260</v>
+      </c>
+      <c r="AA556">
+        <v>2640</v>
+      </c>
+      <c r="AB556">
+        <v>1453</v>
+      </c>
+      <c r="AC556">
+        <v>10042</v>
+      </c>
+      <c r="AD556">
+        <v>4888</v>
+      </c>
+      <c r="AE556">
+        <v>10033</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="587">
   <si>
     <t>date</t>
   </si>
@@ -1772,6 +1772,9 @@
   </si>
   <si>
     <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
   </si>
 </sst>
 </file>
@@ -2114,7 +2117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE556"/>
+  <dimension ref="A1:AE557"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -54676,6 +54679,101 @@
         <v>10033</v>
       </c>
     </row>
+    <row r="557" spans="1:31">
+      <c r="A557" t="s">
+        <v>586</v>
+      </c>
+      <c r="B557">
+        <v>430</v>
+      </c>
+      <c r="C557">
+        <v>1768</v>
+      </c>
+      <c r="D557">
+        <v>10001</v>
+      </c>
+      <c r="E557">
+        <v>1663</v>
+      </c>
+      <c r="F557">
+        <v>4442</v>
+      </c>
+      <c r="G557">
+        <v>5337</v>
+      </c>
+      <c r="H557">
+        <v>166</v>
+      </c>
+      <c r="I557">
+        <v>10034</v>
+      </c>
+      <c r="J557">
+        <v>7306</v>
+      </c>
+      <c r="K557">
+        <v>3109</v>
+      </c>
+      <c r="L557">
+        <v>879</v>
+      </c>
+      <c r="M557">
+        <v>1256</v>
+      </c>
+      <c r="N557">
+        <v>0</v>
+      </c>
+      <c r="O557">
+        <v>0</v>
+      </c>
+      <c r="P557">
+        <v>2729</v>
+      </c>
+      <c r="Q557">
+        <v>4344</v>
+      </c>
+      <c r="R557">
+        <v>245</v>
+      </c>
+      <c r="S557">
+        <v>2321</v>
+      </c>
+      <c r="T557">
+        <v>244</v>
+      </c>
+      <c r="U557">
+        <v>613</v>
+      </c>
+      <c r="V557">
+        <v>145</v>
+      </c>
+      <c r="W557">
+        <v>942</v>
+      </c>
+      <c r="X557">
+        <v>1313</v>
+      </c>
+      <c r="Y557">
+        <v>57</v>
+      </c>
+      <c r="Z557">
+        <v>260</v>
+      </c>
+      <c r="AA557">
+        <v>2641</v>
+      </c>
+      <c r="AB557">
+        <v>1453</v>
+      </c>
+      <c r="AC557">
+        <v>10041</v>
+      </c>
+      <c r="AD557">
+        <v>4889</v>
+      </c>
+      <c r="AE557">
+        <v>10033</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="588">
   <si>
     <t>date</t>
   </si>
@@ -1775,6 +1775,9 @@
   </si>
   <si>
     <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
   </si>
 </sst>
 </file>
@@ -2117,7 +2120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE557"/>
+  <dimension ref="A1:AE558"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -54774,6 +54777,101 @@
         <v>10033</v>
       </c>
     </row>
+    <row r="558" spans="1:31">
+      <c r="A558" t="s">
+        <v>587</v>
+      </c>
+      <c r="B558">
+        <v>430</v>
+      </c>
+      <c r="C558">
+        <v>1769</v>
+      </c>
+      <c r="D558">
+        <v>10097</v>
+      </c>
+      <c r="E558">
+        <v>1663</v>
+      </c>
+      <c r="F558">
+        <v>4439</v>
+      </c>
+      <c r="G558">
+        <v>5346</v>
+      </c>
+      <c r="H558">
+        <v>166</v>
+      </c>
+      <c r="I558">
+        <v>10034</v>
+      </c>
+      <c r="J558">
+        <v>7311</v>
+      </c>
+      <c r="K558">
+        <v>3109</v>
+      </c>
+      <c r="L558">
+        <v>878</v>
+      </c>
+      <c r="M558">
+        <v>1256</v>
+      </c>
+      <c r="N558">
+        <v>0</v>
+      </c>
+      <c r="O558">
+        <v>0</v>
+      </c>
+      <c r="P558">
+        <v>2729</v>
+      </c>
+      <c r="Q558">
+        <v>4344</v>
+      </c>
+      <c r="R558">
+        <v>245</v>
+      </c>
+      <c r="S558">
+        <v>2321</v>
+      </c>
+      <c r="T558">
+        <v>244</v>
+      </c>
+      <c r="U558">
+        <v>613</v>
+      </c>
+      <c r="V558">
+        <v>145</v>
+      </c>
+      <c r="W558">
+        <v>942</v>
+      </c>
+      <c r="X558">
+        <v>1312</v>
+      </c>
+      <c r="Y558">
+        <v>57</v>
+      </c>
+      <c r="Z558">
+        <v>260</v>
+      </c>
+      <c r="AA558">
+        <v>2641</v>
+      </c>
+      <c r="AB558">
+        <v>1453</v>
+      </c>
+      <c r="AC558">
+        <v>10042</v>
+      </c>
+      <c r="AD558">
+        <v>4894</v>
+      </c>
+      <c r="AE558">
+        <v>10033</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
   <si>
     <t>date</t>
   </si>
@@ -1778,6 +1778,9 @@
   </si>
   <si>
     <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
   </si>
 </sst>
 </file>
@@ -2120,7 +2123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE558"/>
+  <dimension ref="A1:AE559"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -54872,6 +54875,101 @@
         <v>10033</v>
       </c>
     </row>
+    <row r="559" spans="1:31">
+      <c r="A559" t="s">
+        <v>588</v>
+      </c>
+      <c r="B559">
+        <v>431</v>
+      </c>
+      <c r="C559">
+        <v>1770</v>
+      </c>
+      <c r="D559">
+        <v>10052</v>
+      </c>
+      <c r="E559">
+        <v>1663</v>
+      </c>
+      <c r="F559">
+        <v>4441</v>
+      </c>
+      <c r="G559">
+        <v>5350</v>
+      </c>
+      <c r="H559">
+        <v>166</v>
+      </c>
+      <c r="I559">
+        <v>10035</v>
+      </c>
+      <c r="J559">
+        <v>7316</v>
+      </c>
+      <c r="K559">
+        <v>3110</v>
+      </c>
+      <c r="L559">
+        <v>877</v>
+      </c>
+      <c r="M559">
+        <v>1256</v>
+      </c>
+      <c r="N559">
+        <v>0</v>
+      </c>
+      <c r="O559">
+        <v>0</v>
+      </c>
+      <c r="P559">
+        <v>2729</v>
+      </c>
+      <c r="Q559">
+        <v>4341</v>
+      </c>
+      <c r="R559">
+        <v>245</v>
+      </c>
+      <c r="S559">
+        <v>2322</v>
+      </c>
+      <c r="T559">
+        <v>243</v>
+      </c>
+      <c r="U559">
+        <v>613</v>
+      </c>
+      <c r="V559">
+        <v>145</v>
+      </c>
+      <c r="W559">
+        <v>942</v>
+      </c>
+      <c r="X559">
+        <v>1312</v>
+      </c>
+      <c r="Y559">
+        <v>57</v>
+      </c>
+      <c r="Z559">
+        <v>260</v>
+      </c>
+      <c r="AA559">
+        <v>2639</v>
+      </c>
+      <c r="AB559">
+        <v>1453</v>
+      </c>
+      <c r="AC559">
+        <v>10042</v>
+      </c>
+      <c r="AD559">
+        <v>4895</v>
+      </c>
+      <c r="AE559">
+        <v>10032</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
   <si>
     <t>date</t>
   </si>
@@ -1781,6 +1781,9 @@
   </si>
   <si>
     <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
   </si>
 </sst>
 </file>
@@ -2123,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE559"/>
+  <dimension ref="A1:AE560"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -54970,6 +54973,101 @@
         <v>10032</v>
       </c>
     </row>
+    <row r="560" spans="1:31">
+      <c r="A560" t="s">
+        <v>589</v>
+      </c>
+      <c r="B560">
+        <v>431</v>
+      </c>
+      <c r="C560">
+        <v>1770</v>
+      </c>
+      <c r="D560">
+        <v>10049</v>
+      </c>
+      <c r="E560">
+        <v>1663</v>
+      </c>
+      <c r="F560">
+        <v>4440</v>
+      </c>
+      <c r="G560">
+        <v>5361</v>
+      </c>
+      <c r="H560">
+        <v>166</v>
+      </c>
+      <c r="I560">
+        <v>10038</v>
+      </c>
+      <c r="J560">
+        <v>7317</v>
+      </c>
+      <c r="K560">
+        <v>3109</v>
+      </c>
+      <c r="L560">
+        <v>877</v>
+      </c>
+      <c r="M560">
+        <v>1256</v>
+      </c>
+      <c r="N560">
+        <v>0</v>
+      </c>
+      <c r="O560">
+        <v>0</v>
+      </c>
+      <c r="P560">
+        <v>2729</v>
+      </c>
+      <c r="Q560">
+        <v>4342</v>
+      </c>
+      <c r="R560">
+        <v>245</v>
+      </c>
+      <c r="S560">
+        <v>2323</v>
+      </c>
+      <c r="T560">
+        <v>243</v>
+      </c>
+      <c r="U560">
+        <v>613</v>
+      </c>
+      <c r="V560">
+        <v>145</v>
+      </c>
+      <c r="W560">
+        <v>943</v>
+      </c>
+      <c r="X560">
+        <v>1312</v>
+      </c>
+      <c r="Y560">
+        <v>57</v>
+      </c>
+      <c r="Z560">
+        <v>260</v>
+      </c>
+      <c r="AA560">
+        <v>2639</v>
+      </c>
+      <c r="AB560">
+        <v>1454</v>
+      </c>
+      <c r="AC560">
+        <v>10044</v>
+      </c>
+      <c r="AD560">
+        <v>4897</v>
+      </c>
+      <c r="AE560">
+        <v>10030</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="591">
   <si>
     <t>date</t>
   </si>
@@ -1784,6 +1784,9 @@
   </si>
   <si>
     <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
   </si>
 </sst>
 </file>
@@ -2126,7 +2129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE560"/>
+  <dimension ref="A1:AE561"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55068,6 +55071,101 @@
         <v>10030</v>
       </c>
     </row>
+    <row r="561" spans="1:31">
+      <c r="A561" t="s">
+        <v>590</v>
+      </c>
+      <c r="B561">
+        <v>431</v>
+      </c>
+      <c r="C561">
+        <v>1770</v>
+      </c>
+      <c r="D561">
+        <v>10050</v>
+      </c>
+      <c r="E561">
+        <v>1664</v>
+      </c>
+      <c r="F561">
+        <v>4441</v>
+      </c>
+      <c r="G561">
+        <v>5366</v>
+      </c>
+      <c r="H561">
+        <v>166</v>
+      </c>
+      <c r="I561">
+        <v>10040</v>
+      </c>
+      <c r="J561">
+        <v>7319</v>
+      </c>
+      <c r="K561">
+        <v>3108</v>
+      </c>
+      <c r="L561">
+        <v>877</v>
+      </c>
+      <c r="M561">
+        <v>1256</v>
+      </c>
+      <c r="N561">
+        <v>0</v>
+      </c>
+      <c r="O561">
+        <v>0</v>
+      </c>
+      <c r="P561">
+        <v>2729</v>
+      </c>
+      <c r="Q561">
+        <v>4343</v>
+      </c>
+      <c r="R561">
+        <v>245</v>
+      </c>
+      <c r="S561">
+        <v>2324</v>
+      </c>
+      <c r="T561">
+        <v>243</v>
+      </c>
+      <c r="U561">
+        <v>613</v>
+      </c>
+      <c r="V561">
+        <v>145</v>
+      </c>
+      <c r="W561">
+        <v>943</v>
+      </c>
+      <c r="X561">
+        <v>1313</v>
+      </c>
+      <c r="Y561">
+        <v>57</v>
+      </c>
+      <c r="Z561">
+        <v>260</v>
+      </c>
+      <c r="AA561">
+        <v>2639</v>
+      </c>
+      <c r="AB561">
+        <v>1454</v>
+      </c>
+      <c r="AC561">
+        <v>10045</v>
+      </c>
+      <c r="AD561">
+        <v>4898</v>
+      </c>
+      <c r="AE561">
+        <v>10032</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
   <si>
     <t>date</t>
   </si>
@@ -1787,6 +1787,9 @@
   </si>
   <si>
     <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
   </si>
 </sst>
 </file>
@@ -2129,7 +2132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE561"/>
+  <dimension ref="A1:AE562"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55166,6 +55169,101 @@
         <v>10032</v>
       </c>
     </row>
+    <row r="562" spans="1:31">
+      <c r="A562" t="s">
+        <v>591</v>
+      </c>
+      <c r="B562">
+        <v>431</v>
+      </c>
+      <c r="C562">
+        <v>1769</v>
+      </c>
+      <c r="D562">
+        <v>10049</v>
+      </c>
+      <c r="E562">
+        <v>1664</v>
+      </c>
+      <c r="F562">
+        <v>4441</v>
+      </c>
+      <c r="G562">
+        <v>5369</v>
+      </c>
+      <c r="H562">
+        <v>165</v>
+      </c>
+      <c r="I562">
+        <v>10039</v>
+      </c>
+      <c r="J562">
+        <v>7320</v>
+      </c>
+      <c r="K562">
+        <v>3106</v>
+      </c>
+      <c r="L562">
+        <v>877</v>
+      </c>
+      <c r="M562">
+        <v>1256</v>
+      </c>
+      <c r="N562">
+        <v>0</v>
+      </c>
+      <c r="O562">
+        <v>0</v>
+      </c>
+      <c r="P562">
+        <v>2730</v>
+      </c>
+      <c r="Q562">
+        <v>4343</v>
+      </c>
+      <c r="R562">
+        <v>245</v>
+      </c>
+      <c r="S562">
+        <v>2324</v>
+      </c>
+      <c r="T562">
+        <v>243</v>
+      </c>
+      <c r="U562">
+        <v>612</v>
+      </c>
+      <c r="V562">
+        <v>145</v>
+      </c>
+      <c r="W562">
+        <v>943</v>
+      </c>
+      <c r="X562">
+        <v>1314</v>
+      </c>
+      <c r="Y562">
+        <v>57</v>
+      </c>
+      <c r="Z562">
+        <v>260</v>
+      </c>
+      <c r="AA562">
+        <v>2638</v>
+      </c>
+      <c r="AB562">
+        <v>1452</v>
+      </c>
+      <c r="AC562">
+        <v>10044</v>
+      </c>
+      <c r="AD562">
+        <v>4898</v>
+      </c>
+      <c r="AE562">
+        <v>10031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="593">
   <si>
     <t>date</t>
   </si>
@@ -1790,6 +1790,9 @@
   </si>
   <si>
     <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
   </si>
 </sst>
 </file>
@@ -2132,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE562"/>
+  <dimension ref="A1:AE563"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55264,6 +55267,101 @@
         <v>10031</v>
       </c>
     </row>
+    <row r="563" spans="1:31">
+      <c r="A563" t="s">
+        <v>592</v>
+      </c>
+      <c r="B563">
+        <v>433</v>
+      </c>
+      <c r="C563">
+        <v>1771</v>
+      </c>
+      <c r="D563">
+        <v>10045</v>
+      </c>
+      <c r="E563">
+        <v>1665</v>
+      </c>
+      <c r="F563">
+        <v>4441</v>
+      </c>
+      <c r="G563">
+        <v>5371</v>
+      </c>
+      <c r="H563">
+        <v>165</v>
+      </c>
+      <c r="I563">
+        <v>10040</v>
+      </c>
+      <c r="J563">
+        <v>7317</v>
+      </c>
+      <c r="K563">
+        <v>3105</v>
+      </c>
+      <c r="L563">
+        <v>877</v>
+      </c>
+      <c r="M563">
+        <v>1256</v>
+      </c>
+      <c r="N563">
+        <v>0</v>
+      </c>
+      <c r="O563">
+        <v>0</v>
+      </c>
+      <c r="P563">
+        <v>2730</v>
+      </c>
+      <c r="Q563">
+        <v>4343</v>
+      </c>
+      <c r="R563">
+        <v>245</v>
+      </c>
+      <c r="S563">
+        <v>2325</v>
+      </c>
+      <c r="T563">
+        <v>243</v>
+      </c>
+      <c r="U563">
+        <v>612</v>
+      </c>
+      <c r="V563">
+        <v>145</v>
+      </c>
+      <c r="W563">
+        <v>944</v>
+      </c>
+      <c r="X563">
+        <v>1314</v>
+      </c>
+      <c r="Y563">
+        <v>57</v>
+      </c>
+      <c r="Z563">
+        <v>260</v>
+      </c>
+      <c r="AA563">
+        <v>2638</v>
+      </c>
+      <c r="AB563">
+        <v>1453</v>
+      </c>
+      <c r="AC563">
+        <v>10044</v>
+      </c>
+      <c r="AD563">
+        <v>4896</v>
+      </c>
+      <c r="AE563">
+        <v>10031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="594">
   <si>
     <t>date</t>
   </si>
@@ -1793,6 +1793,9 @@
   </si>
   <si>
     <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE563"/>
+  <dimension ref="A1:AE564"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55362,6 +55365,101 @@
         <v>10031</v>
       </c>
     </row>
+    <row r="564" spans="1:31">
+      <c r="A564" t="s">
+        <v>593</v>
+      </c>
+      <c r="B564">
+        <v>434</v>
+      </c>
+      <c r="C564">
+        <v>1772</v>
+      </c>
+      <c r="D564">
+        <v>10042</v>
+      </c>
+      <c r="E564">
+        <v>1666</v>
+      </c>
+      <c r="F564">
+        <v>4442</v>
+      </c>
+      <c r="G564">
+        <v>5369</v>
+      </c>
+      <c r="H564">
+        <v>165</v>
+      </c>
+      <c r="I564">
+        <v>10038</v>
+      </c>
+      <c r="J564">
+        <v>7317</v>
+      </c>
+      <c r="K564">
+        <v>3106</v>
+      </c>
+      <c r="L564">
+        <v>877</v>
+      </c>
+      <c r="M564">
+        <v>1256</v>
+      </c>
+      <c r="N564">
+        <v>0</v>
+      </c>
+      <c r="O564">
+        <v>0</v>
+      </c>
+      <c r="P564">
+        <v>2731</v>
+      </c>
+      <c r="Q564">
+        <v>4345</v>
+      </c>
+      <c r="R564">
+        <v>245</v>
+      </c>
+      <c r="S564">
+        <v>2325</v>
+      </c>
+      <c r="T564">
+        <v>243</v>
+      </c>
+      <c r="U564">
+        <v>612</v>
+      </c>
+      <c r="V564">
+        <v>145</v>
+      </c>
+      <c r="W564">
+        <v>944</v>
+      </c>
+      <c r="X564">
+        <v>1315</v>
+      </c>
+      <c r="Y564">
+        <v>57</v>
+      </c>
+      <c r="Z564">
+        <v>259</v>
+      </c>
+      <c r="AA564">
+        <v>2640</v>
+      </c>
+      <c r="AB564">
+        <v>1452</v>
+      </c>
+      <c r="AC564">
+        <v>10044</v>
+      </c>
+      <c r="AD564">
+        <v>4896</v>
+      </c>
+      <c r="AE564">
+        <v>10031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="595">
   <si>
     <t>date</t>
   </si>
@@ -1796,6 +1796,9 @@
   </si>
   <si>
     <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
   </si>
 </sst>
 </file>
@@ -2138,7 +2141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE564"/>
+  <dimension ref="A1:AE565"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55460,6 +55463,101 @@
         <v>10031</v>
       </c>
     </row>
+    <row r="565" spans="1:31">
+      <c r="A565" t="s">
+        <v>594</v>
+      </c>
+      <c r="B565">
+        <v>434</v>
+      </c>
+      <c r="C565">
+        <v>1773</v>
+      </c>
+      <c r="D565">
+        <v>10039</v>
+      </c>
+      <c r="E565">
+        <v>1665</v>
+      </c>
+      <c r="F565">
+        <v>4443</v>
+      </c>
+      <c r="G565">
+        <v>5370</v>
+      </c>
+      <c r="H565">
+        <v>165</v>
+      </c>
+      <c r="I565">
+        <v>10037</v>
+      </c>
+      <c r="J565">
+        <v>7325</v>
+      </c>
+      <c r="K565">
+        <v>3106</v>
+      </c>
+      <c r="L565">
+        <v>877</v>
+      </c>
+      <c r="M565">
+        <v>1256</v>
+      </c>
+      <c r="N565">
+        <v>0</v>
+      </c>
+      <c r="O565">
+        <v>0</v>
+      </c>
+      <c r="P565">
+        <v>2732</v>
+      </c>
+      <c r="Q565">
+        <v>4346</v>
+      </c>
+      <c r="R565">
+        <v>245</v>
+      </c>
+      <c r="S565">
+        <v>2325</v>
+      </c>
+      <c r="T565">
+        <v>244</v>
+      </c>
+      <c r="U565">
+        <v>612</v>
+      </c>
+      <c r="V565">
+        <v>145</v>
+      </c>
+      <c r="W565">
+        <v>944</v>
+      </c>
+      <c r="X565">
+        <v>1315</v>
+      </c>
+      <c r="Y565">
+        <v>57</v>
+      </c>
+      <c r="Z565">
+        <v>259</v>
+      </c>
+      <c r="AA565">
+        <v>2642</v>
+      </c>
+      <c r="AB565">
+        <v>1452</v>
+      </c>
+      <c r="AC565">
+        <v>10044</v>
+      </c>
+      <c r="AD565">
+        <v>4895</v>
+      </c>
+      <c r="AE565">
+        <v>10031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="596">
   <si>
     <t>date</t>
   </si>
@@ -1799,6 +1799,9 @@
   </si>
   <si>
     <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
   </si>
 </sst>
 </file>
@@ -2141,7 +2144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE565"/>
+  <dimension ref="A1:AE566"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55558,6 +55561,101 @@
         <v>10031</v>
       </c>
     </row>
+    <row r="566" spans="1:31">
+      <c r="A566" t="s">
+        <v>595</v>
+      </c>
+      <c r="B566">
+        <v>433</v>
+      </c>
+      <c r="C566">
+        <v>1773</v>
+      </c>
+      <c r="D566">
+        <v>10038</v>
+      </c>
+      <c r="E566">
+        <v>1665</v>
+      </c>
+      <c r="F566">
+        <v>4447</v>
+      </c>
+      <c r="G566">
+        <v>5372</v>
+      </c>
+      <c r="H566">
+        <v>164</v>
+      </c>
+      <c r="I566">
+        <v>10038</v>
+      </c>
+      <c r="J566">
+        <v>7331</v>
+      </c>
+      <c r="K566">
+        <v>3105</v>
+      </c>
+      <c r="L566">
+        <v>878</v>
+      </c>
+      <c r="M566">
+        <v>1256</v>
+      </c>
+      <c r="N566">
+        <v>0</v>
+      </c>
+      <c r="O566">
+        <v>0</v>
+      </c>
+      <c r="P566">
+        <v>2732</v>
+      </c>
+      <c r="Q566">
+        <v>4349</v>
+      </c>
+      <c r="R566">
+        <v>245</v>
+      </c>
+      <c r="S566">
+        <v>2325</v>
+      </c>
+      <c r="T566">
+        <v>244</v>
+      </c>
+      <c r="U566">
+        <v>612</v>
+      </c>
+      <c r="V566">
+        <v>145</v>
+      </c>
+      <c r="W566">
+        <v>943</v>
+      </c>
+      <c r="X566">
+        <v>1315</v>
+      </c>
+      <c r="Y566">
+        <v>57</v>
+      </c>
+      <c r="Z566">
+        <v>259</v>
+      </c>
+      <c r="AA566">
+        <v>2642</v>
+      </c>
+      <c r="AB566">
+        <v>1452</v>
+      </c>
+      <c r="AC566">
+        <v>10042</v>
+      </c>
+      <c r="AD566">
+        <v>4897</v>
+      </c>
+      <c r="AE566">
+        <v>10029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="597">
   <si>
     <t>date</t>
   </si>
@@ -1802,6 +1802,9 @@
   </si>
   <si>
     <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
   </si>
 </sst>
 </file>
@@ -2144,7 +2147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE566"/>
+  <dimension ref="A1:AE567"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55656,6 +55659,101 @@
         <v>10029</v>
       </c>
     </row>
+    <row r="567" spans="1:31">
+      <c r="A567" t="s">
+        <v>596</v>
+      </c>
+      <c r="B567">
+        <v>435</v>
+      </c>
+      <c r="C567">
+        <v>1773</v>
+      </c>
+      <c r="D567">
+        <v>10088</v>
+      </c>
+      <c r="E567">
+        <v>1665</v>
+      </c>
+      <c r="F567">
+        <v>4448</v>
+      </c>
+      <c r="G567">
+        <v>5374</v>
+      </c>
+      <c r="H567">
+        <v>164</v>
+      </c>
+      <c r="I567">
+        <v>10037</v>
+      </c>
+      <c r="J567">
+        <v>7334</v>
+      </c>
+      <c r="K567">
+        <v>3107</v>
+      </c>
+      <c r="L567">
+        <v>880</v>
+      </c>
+      <c r="M567">
+        <v>1256</v>
+      </c>
+      <c r="N567">
+        <v>0</v>
+      </c>
+      <c r="O567">
+        <v>0</v>
+      </c>
+      <c r="P567">
+        <v>2733</v>
+      </c>
+      <c r="Q567">
+        <v>4351</v>
+      </c>
+      <c r="R567">
+        <v>245</v>
+      </c>
+      <c r="S567">
+        <v>2326</v>
+      </c>
+      <c r="T567">
+        <v>244</v>
+      </c>
+      <c r="U567">
+        <v>612</v>
+      </c>
+      <c r="V567">
+        <v>145</v>
+      </c>
+      <c r="W567">
+        <v>944</v>
+      </c>
+      <c r="X567">
+        <v>1315</v>
+      </c>
+      <c r="Y567">
+        <v>58</v>
+      </c>
+      <c r="Z567">
+        <v>260</v>
+      </c>
+      <c r="AA567">
+        <v>2645</v>
+      </c>
+      <c r="AB567">
+        <v>1452</v>
+      </c>
+      <c r="AC567">
+        <v>10042</v>
+      </c>
+      <c r="AD567">
+        <v>4896</v>
+      </c>
+      <c r="AE567">
+        <v>10029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="598">
   <si>
     <t>date</t>
   </si>
@@ -1805,6 +1805,9 @@
   </si>
   <si>
     <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
   </si>
 </sst>
 </file>
@@ -2147,7 +2150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE567"/>
+  <dimension ref="A1:AE568"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55754,6 +55757,101 @@
         <v>10029</v>
       </c>
     </row>
+    <row r="568" spans="1:31">
+      <c r="A568" t="s">
+        <v>597</v>
+      </c>
+      <c r="B568">
+        <v>435</v>
+      </c>
+      <c r="C568">
+        <v>1773</v>
+      </c>
+      <c r="D568">
+        <v>10088</v>
+      </c>
+      <c r="E568">
+        <v>1666</v>
+      </c>
+      <c r="F568">
+        <v>4450</v>
+      </c>
+      <c r="G568">
+        <v>5376</v>
+      </c>
+      <c r="H568">
+        <v>163</v>
+      </c>
+      <c r="I568">
+        <v>10038</v>
+      </c>
+      <c r="J568">
+        <v>7333</v>
+      </c>
+      <c r="K568">
+        <v>3109</v>
+      </c>
+      <c r="L568">
+        <v>881</v>
+      </c>
+      <c r="M568">
+        <v>1257</v>
+      </c>
+      <c r="N568">
+        <v>0</v>
+      </c>
+      <c r="O568">
+        <v>0</v>
+      </c>
+      <c r="P568">
+        <v>2733</v>
+      </c>
+      <c r="Q568">
+        <v>4349</v>
+      </c>
+      <c r="R568">
+        <v>245</v>
+      </c>
+      <c r="S568">
+        <v>2327</v>
+      </c>
+      <c r="T568">
+        <v>244</v>
+      </c>
+      <c r="U568">
+        <v>612</v>
+      </c>
+      <c r="V568">
+        <v>145</v>
+      </c>
+      <c r="W568">
+        <v>946</v>
+      </c>
+      <c r="X568">
+        <v>1316</v>
+      </c>
+      <c r="Y568">
+        <v>58</v>
+      </c>
+      <c r="Z568">
+        <v>260</v>
+      </c>
+      <c r="AA568">
+        <v>2643</v>
+      </c>
+      <c r="AB568">
+        <v>1453</v>
+      </c>
+      <c r="AC568">
+        <v>10043</v>
+      </c>
+      <c r="AD568">
+        <v>4895</v>
+      </c>
+      <c r="AE568">
+        <v>10030</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="599">
   <si>
     <t>date</t>
   </si>
@@ -1808,6 +1808,9 @@
   </si>
   <si>
     <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
   </si>
 </sst>
 </file>
@@ -2150,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE568"/>
+  <dimension ref="A1:AE569"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55852,6 +55855,101 @@
         <v>10030</v>
       </c>
     </row>
+    <row r="569" spans="1:31">
+      <c r="A569" t="s">
+        <v>598</v>
+      </c>
+      <c r="B569">
+        <v>435</v>
+      </c>
+      <c r="C569">
+        <v>1773</v>
+      </c>
+      <c r="D569">
+        <v>10044</v>
+      </c>
+      <c r="E569">
+        <v>1666</v>
+      </c>
+      <c r="F569">
+        <v>4447</v>
+      </c>
+      <c r="G569">
+        <v>5374</v>
+      </c>
+      <c r="H569">
+        <v>163</v>
+      </c>
+      <c r="I569">
+        <v>10039</v>
+      </c>
+      <c r="J569">
+        <v>7334</v>
+      </c>
+      <c r="K569">
+        <v>3109</v>
+      </c>
+      <c r="L569">
+        <v>881</v>
+      </c>
+      <c r="M569">
+        <v>1259</v>
+      </c>
+      <c r="N569">
+        <v>0</v>
+      </c>
+      <c r="O569">
+        <v>0</v>
+      </c>
+      <c r="P569">
+        <v>2734</v>
+      </c>
+      <c r="Q569">
+        <v>4351</v>
+      </c>
+      <c r="R569">
+        <v>245</v>
+      </c>
+      <c r="S569">
+        <v>2327</v>
+      </c>
+      <c r="T569">
+        <v>244</v>
+      </c>
+      <c r="U569">
+        <v>612</v>
+      </c>
+      <c r="V569">
+        <v>145</v>
+      </c>
+      <c r="W569">
+        <v>945</v>
+      </c>
+      <c r="X569">
+        <v>1316</v>
+      </c>
+      <c r="Y569">
+        <v>58</v>
+      </c>
+      <c r="Z569">
+        <v>260</v>
+      </c>
+      <c r="AA569">
+        <v>2643</v>
+      </c>
+      <c r="AB569">
+        <v>1455</v>
+      </c>
+      <c r="AC569">
+        <v>10042</v>
+      </c>
+      <c r="AD569">
+        <v>4894</v>
+      </c>
+      <c r="AE569">
+        <v>10030</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="600">
   <si>
     <t>date</t>
   </si>
@@ -1811,6 +1811,9 @@
   </si>
   <si>
     <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
   </si>
 </sst>
 </file>
@@ -2153,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE569"/>
+  <dimension ref="A1:AE570"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -55950,6 +55953,101 @@
         <v>10030</v>
       </c>
     </row>
+    <row r="570" spans="1:31">
+      <c r="A570" t="s">
+        <v>599</v>
+      </c>
+      <c r="B570">
+        <v>435</v>
+      </c>
+      <c r="C570">
+        <v>1773</v>
+      </c>
+      <c r="D570">
+        <v>10045</v>
+      </c>
+      <c r="E570">
+        <v>1666</v>
+      </c>
+      <c r="F570">
+        <v>4447</v>
+      </c>
+      <c r="G570">
+        <v>5375</v>
+      </c>
+      <c r="H570">
+        <v>163</v>
+      </c>
+      <c r="I570">
+        <v>10038</v>
+      </c>
+      <c r="J570">
+        <v>7338</v>
+      </c>
+      <c r="K570">
+        <v>3108</v>
+      </c>
+      <c r="L570">
+        <v>882</v>
+      </c>
+      <c r="M570">
+        <v>1259</v>
+      </c>
+      <c r="N570">
+        <v>0</v>
+      </c>
+      <c r="O570">
+        <v>0</v>
+      </c>
+      <c r="P570">
+        <v>2731</v>
+      </c>
+      <c r="Q570">
+        <v>4350</v>
+      </c>
+      <c r="R570">
+        <v>245</v>
+      </c>
+      <c r="S570">
+        <v>2327</v>
+      </c>
+      <c r="T570">
+        <v>244</v>
+      </c>
+      <c r="U570">
+        <v>612</v>
+      </c>
+      <c r="V570">
+        <v>145</v>
+      </c>
+      <c r="W570">
+        <v>945</v>
+      </c>
+      <c r="X570">
+        <v>1317</v>
+      </c>
+      <c r="Y570">
+        <v>58</v>
+      </c>
+      <c r="Z570">
+        <v>260</v>
+      </c>
+      <c r="AA570">
+        <v>2644</v>
+      </c>
+      <c r="AB570">
+        <v>1455</v>
+      </c>
+      <c r="AC570">
+        <v>10038</v>
+      </c>
+      <c r="AD570">
+        <v>4894</v>
+      </c>
+      <c r="AE570">
+        <v>10029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="601">
   <si>
     <t>date</t>
   </si>
@@ -1814,6 +1814,9 @@
   </si>
   <si>
     <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
   </si>
 </sst>
 </file>
@@ -2156,7 +2159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE570"/>
+  <dimension ref="A1:AE571"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56048,6 +56051,101 @@
         <v>10029</v>
       </c>
     </row>
+    <row r="571" spans="1:31">
+      <c r="A571" t="s">
+        <v>600</v>
+      </c>
+      <c r="B571">
+        <v>435</v>
+      </c>
+      <c r="C571">
+        <v>1773</v>
+      </c>
+      <c r="D571">
+        <v>10044</v>
+      </c>
+      <c r="E571">
+        <v>1666</v>
+      </c>
+      <c r="F571">
+        <v>4445</v>
+      </c>
+      <c r="G571">
+        <v>5377</v>
+      </c>
+      <c r="H571">
+        <v>163</v>
+      </c>
+      <c r="I571">
+        <v>10037</v>
+      </c>
+      <c r="J571">
+        <v>7339</v>
+      </c>
+      <c r="K571">
+        <v>3107</v>
+      </c>
+      <c r="L571">
+        <v>882</v>
+      </c>
+      <c r="M571">
+        <v>1258</v>
+      </c>
+      <c r="N571">
+        <v>0</v>
+      </c>
+      <c r="O571">
+        <v>0</v>
+      </c>
+      <c r="P571">
+        <v>2731</v>
+      </c>
+      <c r="Q571">
+        <v>4348</v>
+      </c>
+      <c r="R571">
+        <v>245</v>
+      </c>
+      <c r="S571">
+        <v>2327</v>
+      </c>
+      <c r="T571">
+        <v>244</v>
+      </c>
+      <c r="U571">
+        <v>611</v>
+      </c>
+      <c r="V571">
+        <v>146</v>
+      </c>
+      <c r="W571">
+        <v>945</v>
+      </c>
+      <c r="X571">
+        <v>1317</v>
+      </c>
+      <c r="Y571">
+        <v>58</v>
+      </c>
+      <c r="Z571">
+        <v>261</v>
+      </c>
+      <c r="AA571">
+        <v>2644</v>
+      </c>
+      <c r="AB571">
+        <v>1455</v>
+      </c>
+      <c r="AC571">
+        <v>10039</v>
+      </c>
+      <c r="AD571">
+        <v>4896</v>
+      </c>
+      <c r="AE571">
+        <v>10028</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="602">
   <si>
     <t>date</t>
   </si>
@@ -1817,6 +1817,9 @@
   </si>
   <si>
     <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
   </si>
 </sst>
 </file>
@@ -2159,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE571"/>
+  <dimension ref="A1:AE572"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56146,6 +56149,101 @@
         <v>10028</v>
       </c>
     </row>
+    <row r="572" spans="1:31">
+      <c r="A572" t="s">
+        <v>601</v>
+      </c>
+      <c r="B572">
+        <v>436</v>
+      </c>
+      <c r="C572">
+        <v>1774</v>
+      </c>
+      <c r="D572">
+        <v>10039</v>
+      </c>
+      <c r="E572">
+        <v>1665</v>
+      </c>
+      <c r="F572">
+        <v>4446</v>
+      </c>
+      <c r="G572">
+        <v>5379</v>
+      </c>
+      <c r="H572">
+        <v>163</v>
+      </c>
+      <c r="I572">
+        <v>10035</v>
+      </c>
+      <c r="J572">
+        <v>7341</v>
+      </c>
+      <c r="K572">
+        <v>3107</v>
+      </c>
+      <c r="L572">
+        <v>883</v>
+      </c>
+      <c r="M572">
+        <v>1259</v>
+      </c>
+      <c r="N572">
+        <v>0</v>
+      </c>
+      <c r="O572">
+        <v>0</v>
+      </c>
+      <c r="P572">
+        <v>2732</v>
+      </c>
+      <c r="Q572">
+        <v>4350</v>
+      </c>
+      <c r="R572">
+        <v>245</v>
+      </c>
+      <c r="S572">
+        <v>2326</v>
+      </c>
+      <c r="T572">
+        <v>244</v>
+      </c>
+      <c r="U572">
+        <v>612</v>
+      </c>
+      <c r="V572">
+        <v>146</v>
+      </c>
+      <c r="W572">
+        <v>945</v>
+      </c>
+      <c r="X572">
+        <v>1317</v>
+      </c>
+      <c r="Y572">
+        <v>58</v>
+      </c>
+      <c r="Z572">
+        <v>262</v>
+      </c>
+      <c r="AA572">
+        <v>2644</v>
+      </c>
+      <c r="AB572">
+        <v>1455</v>
+      </c>
+      <c r="AC572">
+        <v>10037</v>
+      </c>
+      <c r="AD572">
+        <v>4898</v>
+      </c>
+      <c r="AE572">
+        <v>10030</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="603">
   <si>
     <t>date</t>
   </si>
@@ -1820,6 +1820,9 @@
   </si>
   <si>
     <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
   </si>
 </sst>
 </file>
@@ -2162,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE572"/>
+  <dimension ref="A1:AE573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56244,6 +56247,101 @@
         <v>10030</v>
       </c>
     </row>
+    <row r="573" spans="1:31">
+      <c r="A573" t="s">
+        <v>602</v>
+      </c>
+      <c r="B573">
+        <v>436</v>
+      </c>
+      <c r="C573">
+        <v>1775</v>
+      </c>
+      <c r="D573">
+        <v>10041</v>
+      </c>
+      <c r="E573">
+        <v>1665</v>
+      </c>
+      <c r="F573">
+        <v>4446</v>
+      </c>
+      <c r="G573">
+        <v>5379</v>
+      </c>
+      <c r="H573">
+        <v>163</v>
+      </c>
+      <c r="I573">
+        <v>10036</v>
+      </c>
+      <c r="J573">
+        <v>7342</v>
+      </c>
+      <c r="K573">
+        <v>3107</v>
+      </c>
+      <c r="L573">
+        <v>884</v>
+      </c>
+      <c r="M573">
+        <v>1261</v>
+      </c>
+      <c r="N573">
+        <v>0</v>
+      </c>
+      <c r="O573">
+        <v>0</v>
+      </c>
+      <c r="P573">
+        <v>2731</v>
+      </c>
+      <c r="Q573">
+        <v>4351</v>
+      </c>
+      <c r="R573">
+        <v>245</v>
+      </c>
+      <c r="S573">
+        <v>2326</v>
+      </c>
+      <c r="T573">
+        <v>244</v>
+      </c>
+      <c r="U573">
+        <v>612</v>
+      </c>
+      <c r="V573">
+        <v>146</v>
+      </c>
+      <c r="W573">
+        <v>945</v>
+      </c>
+      <c r="X573">
+        <v>1317</v>
+      </c>
+      <c r="Y573">
+        <v>58</v>
+      </c>
+      <c r="Z573">
+        <v>262</v>
+      </c>
+      <c r="AA573">
+        <v>2644</v>
+      </c>
+      <c r="AB573">
+        <v>1455</v>
+      </c>
+      <c r="AC573">
+        <v>10038</v>
+      </c>
+      <c r="AD573">
+        <v>4898</v>
+      </c>
+      <c r="AE573">
+        <v>10029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="604">
   <si>
     <t>date</t>
   </si>
@@ -1823,6 +1823,9 @@
   </si>
   <si>
     <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
   </si>
 </sst>
 </file>
@@ -2165,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE573"/>
+  <dimension ref="A1:AE574"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56342,6 +56345,101 @@
         <v>10029</v>
       </c>
     </row>
+    <row r="574" spans="1:31">
+      <c r="A574" t="s">
+        <v>603</v>
+      </c>
+      <c r="B574">
+        <v>437</v>
+      </c>
+      <c r="C574">
+        <v>1776</v>
+      </c>
+      <c r="D574">
+        <v>10039</v>
+      </c>
+      <c r="E574">
+        <v>1665</v>
+      </c>
+      <c r="F574">
+        <v>4448</v>
+      </c>
+      <c r="G574">
+        <v>5378</v>
+      </c>
+      <c r="H574">
+        <v>163</v>
+      </c>
+      <c r="I574">
+        <v>10035</v>
+      </c>
+      <c r="J574">
+        <v>7344</v>
+      </c>
+      <c r="K574">
+        <v>3109</v>
+      </c>
+      <c r="L574">
+        <v>882</v>
+      </c>
+      <c r="M574">
+        <v>1262</v>
+      </c>
+      <c r="N574">
+        <v>0</v>
+      </c>
+      <c r="O574">
+        <v>0</v>
+      </c>
+      <c r="P574">
+        <v>2732</v>
+      </c>
+      <c r="Q574">
+        <v>4353</v>
+      </c>
+      <c r="R574">
+        <v>245</v>
+      </c>
+      <c r="S574">
+        <v>2325</v>
+      </c>
+      <c r="T574">
+        <v>244</v>
+      </c>
+      <c r="U574">
+        <v>613</v>
+      </c>
+      <c r="V574">
+        <v>146</v>
+      </c>
+      <c r="W574">
+        <v>945</v>
+      </c>
+      <c r="X574">
+        <v>1318</v>
+      </c>
+      <c r="Y574">
+        <v>58</v>
+      </c>
+      <c r="Z574">
+        <v>263</v>
+      </c>
+      <c r="AA574">
+        <v>2642</v>
+      </c>
+      <c r="AB574">
+        <v>1457</v>
+      </c>
+      <c r="AC574">
+        <v>10038</v>
+      </c>
+      <c r="AD574">
+        <v>4897</v>
+      </c>
+      <c r="AE574">
+        <v>10029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="605">
   <si>
     <t>date</t>
   </si>
@@ -1826,6 +1826,9 @@
   </si>
   <si>
     <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
   </si>
 </sst>
 </file>
@@ -2168,7 +2171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE574"/>
+  <dimension ref="A1:AE575"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56440,6 +56443,101 @@
         <v>10029</v>
       </c>
     </row>
+    <row r="575" spans="1:31">
+      <c r="A575" t="s">
+        <v>604</v>
+      </c>
+      <c r="B575">
+        <v>440</v>
+      </c>
+      <c r="C575">
+        <v>1776</v>
+      </c>
+      <c r="D575">
+        <v>10039</v>
+      </c>
+      <c r="E575">
+        <v>1665</v>
+      </c>
+      <c r="F575">
+        <v>4450</v>
+      </c>
+      <c r="G575">
+        <v>5382</v>
+      </c>
+      <c r="H575">
+        <v>163</v>
+      </c>
+      <c r="I575">
+        <v>10035</v>
+      </c>
+      <c r="J575">
+        <v>7349</v>
+      </c>
+      <c r="K575">
+        <v>3110</v>
+      </c>
+      <c r="L575">
+        <v>882</v>
+      </c>
+      <c r="M575">
+        <v>1262</v>
+      </c>
+      <c r="N575">
+        <v>0</v>
+      </c>
+      <c r="O575">
+        <v>0</v>
+      </c>
+      <c r="P575">
+        <v>2732</v>
+      </c>
+      <c r="Q575">
+        <v>4354</v>
+      </c>
+      <c r="R575">
+        <v>245</v>
+      </c>
+      <c r="S575">
+        <v>2326</v>
+      </c>
+      <c r="T575">
+        <v>244</v>
+      </c>
+      <c r="U575">
+        <v>614</v>
+      </c>
+      <c r="V575">
+        <v>146</v>
+      </c>
+      <c r="W575">
+        <v>946</v>
+      </c>
+      <c r="X575">
+        <v>1317</v>
+      </c>
+      <c r="Y575">
+        <v>58</v>
+      </c>
+      <c r="Z575">
+        <v>263</v>
+      </c>
+      <c r="AA575">
+        <v>2641</v>
+      </c>
+      <c r="AB575">
+        <v>1458</v>
+      </c>
+      <c r="AC575">
+        <v>10039</v>
+      </c>
+      <c r="AD575">
+        <v>4898</v>
+      </c>
+      <c r="AE575">
+        <v>10029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="606">
   <si>
     <t>date</t>
   </si>
@@ -1829,6 +1829,9 @@
   </si>
   <si>
     <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
   </si>
 </sst>
 </file>
@@ -2171,7 +2174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE575"/>
+  <dimension ref="A1:AE576"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56538,6 +56541,101 @@
         <v>10029</v>
       </c>
     </row>
+    <row r="576" spans="1:31">
+      <c r="A576" t="s">
+        <v>605</v>
+      </c>
+      <c r="B576">
+        <v>441</v>
+      </c>
+      <c r="C576">
+        <v>1775</v>
+      </c>
+      <c r="D576">
+        <v>10042</v>
+      </c>
+      <c r="E576">
+        <v>1665</v>
+      </c>
+      <c r="F576">
+        <v>4450</v>
+      </c>
+      <c r="G576">
+        <v>5383</v>
+      </c>
+      <c r="H576">
+        <v>163</v>
+      </c>
+      <c r="I576">
+        <v>10036</v>
+      </c>
+      <c r="J576">
+        <v>7350</v>
+      </c>
+      <c r="K576">
+        <v>3109</v>
+      </c>
+      <c r="L576">
+        <v>882</v>
+      </c>
+      <c r="M576">
+        <v>1262</v>
+      </c>
+      <c r="N576">
+        <v>0</v>
+      </c>
+      <c r="O576">
+        <v>0</v>
+      </c>
+      <c r="P576">
+        <v>2734</v>
+      </c>
+      <c r="Q576">
+        <v>4352</v>
+      </c>
+      <c r="R576">
+        <v>245</v>
+      </c>
+      <c r="S576">
+        <v>2327</v>
+      </c>
+      <c r="T576">
+        <v>244</v>
+      </c>
+      <c r="U576">
+        <v>614</v>
+      </c>
+      <c r="V576">
+        <v>146</v>
+      </c>
+      <c r="W576">
+        <v>946</v>
+      </c>
+      <c r="X576">
+        <v>1319</v>
+      </c>
+      <c r="Y576">
+        <v>58</v>
+      </c>
+      <c r="Z576">
+        <v>263</v>
+      </c>
+      <c r="AA576">
+        <v>2641</v>
+      </c>
+      <c r="AB576">
+        <v>1458</v>
+      </c>
+      <c r="AC576">
+        <v>10038</v>
+      </c>
+      <c r="AD576">
+        <v>4898</v>
+      </c>
+      <c r="AE576">
+        <v>10030</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="607">
   <si>
     <t>date</t>
   </si>
@@ -1832,6 +1832,9 @@
   </si>
   <si>
     <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
   </si>
 </sst>
 </file>
@@ -2174,7 +2177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE576"/>
+  <dimension ref="A1:AE577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56636,6 +56639,101 @@
         <v>10030</v>
       </c>
     </row>
+    <row r="577" spans="1:31">
+      <c r="A577" t="s">
+        <v>606</v>
+      </c>
+      <c r="B577">
+        <v>442</v>
+      </c>
+      <c r="C577">
+        <v>1777</v>
+      </c>
+      <c r="D577">
+        <v>10045</v>
+      </c>
+      <c r="E577">
+        <v>1664</v>
+      </c>
+      <c r="F577">
+        <v>4452</v>
+      </c>
+      <c r="G577">
+        <v>5383</v>
+      </c>
+      <c r="H577">
+        <v>163</v>
+      </c>
+      <c r="I577">
+        <v>10037</v>
+      </c>
+      <c r="J577">
+        <v>7353</v>
+      </c>
+      <c r="K577">
+        <v>3111</v>
+      </c>
+      <c r="L577">
+        <v>880</v>
+      </c>
+      <c r="M577">
+        <v>1262</v>
+      </c>
+      <c r="N577">
+        <v>0</v>
+      </c>
+      <c r="O577">
+        <v>0</v>
+      </c>
+      <c r="P577">
+        <v>2734</v>
+      </c>
+      <c r="Q577">
+        <v>4351</v>
+      </c>
+      <c r="R577">
+        <v>245</v>
+      </c>
+      <c r="S577">
+        <v>2327</v>
+      </c>
+      <c r="T577">
+        <v>244</v>
+      </c>
+      <c r="U577">
+        <v>615</v>
+      </c>
+      <c r="V577">
+        <v>146</v>
+      </c>
+      <c r="W577">
+        <v>945</v>
+      </c>
+      <c r="X577">
+        <v>1316</v>
+      </c>
+      <c r="Y577">
+        <v>58</v>
+      </c>
+      <c r="Z577">
+        <v>262</v>
+      </c>
+      <c r="AA577">
+        <v>2642</v>
+      </c>
+      <c r="AB577">
+        <v>1458</v>
+      </c>
+      <c r="AC577">
+        <v>10037</v>
+      </c>
+      <c r="AD577">
+        <v>4898</v>
+      </c>
+      <c r="AE577">
+        <v>10030</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="608">
   <si>
     <t>date</t>
   </si>
@@ -1835,6 +1835,9 @@
   </si>
   <si>
     <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
   </si>
 </sst>
 </file>
@@ -2177,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE577"/>
+  <dimension ref="A1:AE578"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56734,6 +56737,101 @@
         <v>10030</v>
       </c>
     </row>
+    <row r="578" spans="1:31">
+      <c r="A578" t="s">
+        <v>607</v>
+      </c>
+      <c r="B578">
+        <v>443</v>
+      </c>
+      <c r="C578">
+        <v>1777</v>
+      </c>
+      <c r="D578">
+        <v>10042</v>
+      </c>
+      <c r="E578">
+        <v>1665</v>
+      </c>
+      <c r="F578">
+        <v>4453</v>
+      </c>
+      <c r="G578">
+        <v>5381</v>
+      </c>
+      <c r="H578">
+        <v>163</v>
+      </c>
+      <c r="I578">
+        <v>10034</v>
+      </c>
+      <c r="J578">
+        <v>7353</v>
+      </c>
+      <c r="K578">
+        <v>3111</v>
+      </c>
+      <c r="L578">
+        <v>879</v>
+      </c>
+      <c r="M578">
+        <v>1262</v>
+      </c>
+      <c r="N578">
+        <v>0</v>
+      </c>
+      <c r="O578">
+        <v>0</v>
+      </c>
+      <c r="P578">
+        <v>2733</v>
+      </c>
+      <c r="Q578">
+        <v>4351</v>
+      </c>
+      <c r="R578">
+        <v>245</v>
+      </c>
+      <c r="S578">
+        <v>2327</v>
+      </c>
+      <c r="T578">
+        <v>244</v>
+      </c>
+      <c r="U578">
+        <v>615</v>
+      </c>
+      <c r="V578">
+        <v>146</v>
+      </c>
+      <c r="W578">
+        <v>945</v>
+      </c>
+      <c r="X578">
+        <v>1316</v>
+      </c>
+      <c r="Y578">
+        <v>58</v>
+      </c>
+      <c r="Z578">
+        <v>262</v>
+      </c>
+      <c r="AA578">
+        <v>2642</v>
+      </c>
+      <c r="AB578">
+        <v>1459</v>
+      </c>
+      <c r="AC578">
+        <v>10035</v>
+      </c>
+      <c r="AD578">
+        <v>4899</v>
+      </c>
+      <c r="AE578">
+        <v>10029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="609">
   <si>
     <t>date</t>
   </si>
@@ -1838,6 +1838,9 @@
   </si>
   <si>
     <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
   </si>
 </sst>
 </file>
@@ -2180,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE578"/>
+  <dimension ref="A1:AE579"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56832,6 +56835,101 @@
         <v>10029</v>
       </c>
     </row>
+    <row r="579" spans="1:31">
+      <c r="A579" t="s">
+        <v>608</v>
+      </c>
+      <c r="B579">
+        <v>443</v>
+      </c>
+      <c r="C579">
+        <v>1778</v>
+      </c>
+      <c r="D579">
+        <v>10039</v>
+      </c>
+      <c r="E579">
+        <v>1668</v>
+      </c>
+      <c r="F579">
+        <v>4454</v>
+      </c>
+      <c r="G579">
+        <v>5383</v>
+      </c>
+      <c r="H579">
+        <v>163</v>
+      </c>
+      <c r="I579">
+        <v>10033</v>
+      </c>
+      <c r="J579">
+        <v>7353</v>
+      </c>
+      <c r="K579">
+        <v>3112</v>
+      </c>
+      <c r="L579">
+        <v>879</v>
+      </c>
+      <c r="M579">
+        <v>1261</v>
+      </c>
+      <c r="N579">
+        <v>0</v>
+      </c>
+      <c r="O579">
+        <v>0</v>
+      </c>
+      <c r="P579">
+        <v>2734</v>
+      </c>
+      <c r="Q579">
+        <v>4350</v>
+      </c>
+      <c r="R579">
+        <v>245</v>
+      </c>
+      <c r="S579">
+        <v>2326</v>
+      </c>
+      <c r="T579">
+        <v>244</v>
+      </c>
+      <c r="U579">
+        <v>617</v>
+      </c>
+      <c r="V579">
+        <v>146</v>
+      </c>
+      <c r="W579">
+        <v>945</v>
+      </c>
+      <c r="X579">
+        <v>1318</v>
+      </c>
+      <c r="Y579">
+        <v>58</v>
+      </c>
+      <c r="Z579">
+        <v>262</v>
+      </c>
+      <c r="AA579">
+        <v>2645</v>
+      </c>
+      <c r="AB579">
+        <v>1460</v>
+      </c>
+      <c r="AC579">
+        <v>10037</v>
+      </c>
+      <c r="AD579">
+        <v>4901</v>
+      </c>
+      <c r="AE579">
+        <v>10029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="610">
   <si>
     <t>date</t>
   </si>
@@ -1841,6 +1841,9 @@
   </si>
   <si>
     <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
   </si>
 </sst>
 </file>
@@ -2183,7 +2186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE579"/>
+  <dimension ref="A1:AE580"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -56930,6 +56933,101 @@
         <v>10029</v>
       </c>
     </row>
+    <row r="580" spans="1:31">
+      <c r="A580" t="s">
+        <v>609</v>
+      </c>
+      <c r="B580">
+        <v>442</v>
+      </c>
+      <c r="C580">
+        <v>1778</v>
+      </c>
+      <c r="D580">
+        <v>10043</v>
+      </c>
+      <c r="E580">
+        <v>1668</v>
+      </c>
+      <c r="F580">
+        <v>4454</v>
+      </c>
+      <c r="G580">
+        <v>5383</v>
+      </c>
+      <c r="H580">
+        <v>163</v>
+      </c>
+      <c r="I580">
+        <v>10034</v>
+      </c>
+      <c r="J580">
+        <v>7355</v>
+      </c>
+      <c r="K580">
+        <v>3112</v>
+      </c>
+      <c r="L580">
+        <v>879</v>
+      </c>
+      <c r="M580">
+        <v>1262</v>
+      </c>
+      <c r="N580">
+        <v>0</v>
+      </c>
+      <c r="O580">
+        <v>0</v>
+      </c>
+      <c r="P580">
+        <v>2735</v>
+      </c>
+      <c r="Q580">
+        <v>4351</v>
+      </c>
+      <c r="R580">
+        <v>245</v>
+      </c>
+      <c r="S580">
+        <v>2326</v>
+      </c>
+      <c r="T580">
+        <v>243</v>
+      </c>
+      <c r="U580">
+        <v>617</v>
+      </c>
+      <c r="V580">
+        <v>146</v>
+      </c>
+      <c r="W580">
+        <v>945</v>
+      </c>
+      <c r="X580">
+        <v>1319</v>
+      </c>
+      <c r="Y580">
+        <v>57</v>
+      </c>
+      <c r="Z580">
+        <v>262</v>
+      </c>
+      <c r="AA580">
+        <v>2645</v>
+      </c>
+      <c r="AB580">
+        <v>1460</v>
+      </c>
+      <c r="AC580">
+        <v>10036</v>
+      </c>
+      <c r="AD580">
+        <v>4902</v>
+      </c>
+      <c r="AE580">
+        <v>10031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="611">
   <si>
     <t>date</t>
   </si>
@@ -1844,6 +1844,9 @@
   </si>
   <si>
     <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
   </si>
 </sst>
 </file>
@@ -2186,7 +2189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE580"/>
+  <dimension ref="A1:AE581"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57028,6 +57031,101 @@
         <v>10031</v>
       </c>
     </row>
+    <row r="581" spans="1:31">
+      <c r="A581" t="s">
+        <v>610</v>
+      </c>
+      <c r="B581">
+        <v>442</v>
+      </c>
+      <c r="C581">
+        <v>1777</v>
+      </c>
+      <c r="D581">
+        <v>10038</v>
+      </c>
+      <c r="E581">
+        <v>1668</v>
+      </c>
+      <c r="F581">
+        <v>4451</v>
+      </c>
+      <c r="G581">
+        <v>5386</v>
+      </c>
+      <c r="H581">
+        <v>163</v>
+      </c>
+      <c r="I581">
+        <v>10036</v>
+      </c>
+      <c r="J581">
+        <v>7356</v>
+      </c>
+      <c r="K581">
+        <v>3114</v>
+      </c>
+      <c r="L581">
+        <v>879</v>
+      </c>
+      <c r="M581">
+        <v>1263</v>
+      </c>
+      <c r="N581">
+        <v>0</v>
+      </c>
+      <c r="O581">
+        <v>0</v>
+      </c>
+      <c r="P581">
+        <v>2734</v>
+      </c>
+      <c r="Q581">
+        <v>4352</v>
+      </c>
+      <c r="R581">
+        <v>245</v>
+      </c>
+      <c r="S581">
+        <v>2327</v>
+      </c>
+      <c r="T581">
+        <v>242</v>
+      </c>
+      <c r="U581">
+        <v>617</v>
+      </c>
+      <c r="V581">
+        <v>146</v>
+      </c>
+      <c r="W581">
+        <v>945</v>
+      </c>
+      <c r="X581">
+        <v>1319</v>
+      </c>
+      <c r="Y581">
+        <v>57</v>
+      </c>
+      <c r="Z581">
+        <v>262</v>
+      </c>
+      <c r="AA581">
+        <v>2645</v>
+      </c>
+      <c r="AB581">
+        <v>1461</v>
+      </c>
+      <c r="AC581">
+        <v>10034</v>
+      </c>
+      <c r="AD581">
+        <v>4903</v>
+      </c>
+      <c r="AE581">
+        <v>10031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="612">
   <si>
     <t>date</t>
   </si>
@@ -1847,6 +1847,9 @@
   </si>
   <si>
     <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
   </si>
 </sst>
 </file>
@@ -2189,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE581"/>
+  <dimension ref="A1:AE582"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57126,6 +57129,101 @@
         <v>10031</v>
       </c>
     </row>
+    <row r="582" spans="1:31">
+      <c r="A582" t="s">
+        <v>611</v>
+      </c>
+      <c r="B582">
+        <v>442</v>
+      </c>
+      <c r="C582">
+        <v>1777</v>
+      </c>
+      <c r="D582">
+        <v>10039</v>
+      </c>
+      <c r="E582">
+        <v>1667</v>
+      </c>
+      <c r="F582">
+        <v>4450</v>
+      </c>
+      <c r="G582">
+        <v>5385</v>
+      </c>
+      <c r="H582">
+        <v>162</v>
+      </c>
+      <c r="I582">
+        <v>10033</v>
+      </c>
+      <c r="J582">
+        <v>7361</v>
+      </c>
+      <c r="K582">
+        <v>3112</v>
+      </c>
+      <c r="L582">
+        <v>878</v>
+      </c>
+      <c r="M582">
+        <v>1263</v>
+      </c>
+      <c r="N582">
+        <v>0</v>
+      </c>
+      <c r="O582">
+        <v>0</v>
+      </c>
+      <c r="P582">
+        <v>2735</v>
+      </c>
+      <c r="Q582">
+        <v>4352</v>
+      </c>
+      <c r="R582">
+        <v>245</v>
+      </c>
+      <c r="S582">
+        <v>2327</v>
+      </c>
+      <c r="T582">
+        <v>242</v>
+      </c>
+      <c r="U582">
+        <v>617</v>
+      </c>
+      <c r="V582">
+        <v>146</v>
+      </c>
+      <c r="W582">
+        <v>945</v>
+      </c>
+      <c r="X582">
+        <v>1320</v>
+      </c>
+      <c r="Y582">
+        <v>57</v>
+      </c>
+      <c r="Z582">
+        <v>262</v>
+      </c>
+      <c r="AA582">
+        <v>2646</v>
+      </c>
+      <c r="AB582">
+        <v>1461</v>
+      </c>
+      <c r="AC582">
+        <v>10034</v>
+      </c>
+      <c r="AD582">
+        <v>4903</v>
+      </c>
+      <c r="AE582">
+        <v>10030</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="613">
   <si>
     <t>date</t>
   </si>
@@ -1850,6 +1850,9 @@
   </si>
   <si>
     <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
   </si>
 </sst>
 </file>
@@ -2192,7 +2195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE582"/>
+  <dimension ref="A1:AE583"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57224,6 +57227,101 @@
         <v>10030</v>
       </c>
     </row>
+    <row r="583" spans="1:31">
+      <c r="A583" t="s">
+        <v>612</v>
+      </c>
+      <c r="B583">
+        <v>444</v>
+      </c>
+      <c r="C583">
+        <v>1776</v>
+      </c>
+      <c r="D583">
+        <v>10035</v>
+      </c>
+      <c r="E583">
+        <v>1668</v>
+      </c>
+      <c r="F583">
+        <v>4450</v>
+      </c>
+      <c r="G583">
+        <v>5386</v>
+      </c>
+      <c r="H583">
+        <v>163</v>
+      </c>
+      <c r="I583">
+        <v>10036</v>
+      </c>
+      <c r="J583">
+        <v>7369</v>
+      </c>
+      <c r="K583">
+        <v>3113</v>
+      </c>
+      <c r="L583">
+        <v>878</v>
+      </c>
+      <c r="M583">
+        <v>1263</v>
+      </c>
+      <c r="N583">
+        <v>0</v>
+      </c>
+      <c r="O583">
+        <v>0</v>
+      </c>
+      <c r="P583">
+        <v>2736</v>
+      </c>
+      <c r="Q583">
+        <v>4353</v>
+      </c>
+      <c r="R583">
+        <v>245</v>
+      </c>
+      <c r="S583">
+        <v>2327</v>
+      </c>
+      <c r="T583">
+        <v>242</v>
+      </c>
+      <c r="U583">
+        <v>618</v>
+      </c>
+      <c r="V583">
+        <v>146</v>
+      </c>
+      <c r="W583">
+        <v>947</v>
+      </c>
+      <c r="X583">
+        <v>1320</v>
+      </c>
+      <c r="Y583">
+        <v>57</v>
+      </c>
+      <c r="Z583">
+        <v>262</v>
+      </c>
+      <c r="AA583">
+        <v>2647</v>
+      </c>
+      <c r="AB583">
+        <v>1461</v>
+      </c>
+      <c r="AC583">
+        <v>10034</v>
+      </c>
+      <c r="AD583">
+        <v>4904</v>
+      </c>
+      <c r="AE583">
+        <v>10030</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="614">
   <si>
     <t>date</t>
   </si>
@@ -1853,6 +1853,9 @@
   </si>
   <si>
     <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
   </si>
 </sst>
 </file>
@@ -2195,7 +2198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE583"/>
+  <dimension ref="A1:AE584"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57322,6 +57325,101 @@
         <v>10030</v>
       </c>
     </row>
+    <row r="584" spans="1:31">
+      <c r="A584" t="s">
+        <v>613</v>
+      </c>
+      <c r="B584">
+        <v>445</v>
+      </c>
+      <c r="C584">
+        <v>1775</v>
+      </c>
+      <c r="D584">
+        <v>10028</v>
+      </c>
+      <c r="E584">
+        <v>1669</v>
+      </c>
+      <c r="F584">
+        <v>4450</v>
+      </c>
+      <c r="G584">
+        <v>5384</v>
+      </c>
+      <c r="H584">
+        <v>163</v>
+      </c>
+      <c r="I584">
+        <v>10038</v>
+      </c>
+      <c r="J584">
+        <v>7374</v>
+      </c>
+      <c r="K584">
+        <v>3113</v>
+      </c>
+      <c r="L584">
+        <v>878</v>
+      </c>
+      <c r="M584">
+        <v>1263</v>
+      </c>
+      <c r="N584">
+        <v>0</v>
+      </c>
+      <c r="O584">
+        <v>0</v>
+      </c>
+      <c r="P584">
+        <v>2736</v>
+      </c>
+      <c r="Q584">
+        <v>4349</v>
+      </c>
+      <c r="R584">
+        <v>245</v>
+      </c>
+      <c r="S584">
+        <v>2329</v>
+      </c>
+      <c r="T584">
+        <v>242</v>
+      </c>
+      <c r="U584">
+        <v>620</v>
+      </c>
+      <c r="V584">
+        <v>146</v>
+      </c>
+      <c r="W584">
+        <v>947</v>
+      </c>
+      <c r="X584">
+        <v>1319</v>
+      </c>
+      <c r="Y584">
+        <v>57</v>
+      </c>
+      <c r="Z584">
+        <v>261</v>
+      </c>
+      <c r="AA584">
+        <v>2647</v>
+      </c>
+      <c r="AB584">
+        <v>1461</v>
+      </c>
+      <c r="AC584">
+        <v>10030</v>
+      </c>
+      <c r="AD584">
+        <v>4905</v>
+      </c>
+      <c r="AE584">
+        <v>10029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="615">
   <si>
     <t>date</t>
   </si>
@@ -1856,6 +1856,9 @@
   </si>
   <si>
     <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
   </si>
 </sst>
 </file>
@@ -2198,7 +2201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE584"/>
+  <dimension ref="A1:AE585"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57420,6 +57423,101 @@
         <v>10029</v>
       </c>
     </row>
+    <row r="585" spans="1:31">
+      <c r="A585" t="s">
+        <v>614</v>
+      </c>
+      <c r="B585">
+        <v>445</v>
+      </c>
+      <c r="C585">
+        <v>1775</v>
+      </c>
+      <c r="D585">
+        <v>10018</v>
+      </c>
+      <c r="E585">
+        <v>1669</v>
+      </c>
+      <c r="F585">
+        <v>4449</v>
+      </c>
+      <c r="G585">
+        <v>5381</v>
+      </c>
+      <c r="H585">
+        <v>163</v>
+      </c>
+      <c r="I585">
+        <v>10037</v>
+      </c>
+      <c r="J585">
+        <v>7372</v>
+      </c>
+      <c r="K585">
+        <v>3113</v>
+      </c>
+      <c r="L585">
+        <v>877</v>
+      </c>
+      <c r="M585">
+        <v>1262</v>
+      </c>
+      <c r="N585">
+        <v>0</v>
+      </c>
+      <c r="O585">
+        <v>0</v>
+      </c>
+      <c r="P585">
+        <v>2737</v>
+      </c>
+      <c r="Q585">
+        <v>4346</v>
+      </c>
+      <c r="R585">
+        <v>245</v>
+      </c>
+      <c r="S585">
+        <v>2329</v>
+      </c>
+      <c r="T585">
+        <v>242</v>
+      </c>
+      <c r="U585">
+        <v>622</v>
+      </c>
+      <c r="V585">
+        <v>146</v>
+      </c>
+      <c r="W585">
+        <v>947</v>
+      </c>
+      <c r="X585">
+        <v>1318</v>
+      </c>
+      <c r="Y585">
+        <v>57</v>
+      </c>
+      <c r="Z585">
+        <v>261</v>
+      </c>
+      <c r="AA585">
+        <v>2646</v>
+      </c>
+      <c r="AB585">
+        <v>1460</v>
+      </c>
+      <c r="AC585">
+        <v>10033</v>
+      </c>
+      <c r="AD585">
+        <v>4907</v>
+      </c>
+      <c r="AE585">
+        <v>10026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="616">
   <si>
     <t>date</t>
   </si>
@@ -1859,6 +1859,9 @@
   </si>
   <si>
     <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
   </si>
 </sst>
 </file>
@@ -2201,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE585"/>
+  <dimension ref="A1:AE586"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57518,6 +57521,101 @@
         <v>10026</v>
       </c>
     </row>
+    <row r="586" spans="1:31">
+      <c r="A586" t="s">
+        <v>615</v>
+      </c>
+      <c r="B586">
+        <v>446</v>
+      </c>
+      <c r="C586">
+        <v>1776</v>
+      </c>
+      <c r="D586">
+        <v>10022</v>
+      </c>
+      <c r="E586">
+        <v>1669</v>
+      </c>
+      <c r="F586">
+        <v>4450</v>
+      </c>
+      <c r="G586">
+        <v>5387</v>
+      </c>
+      <c r="H586">
+        <v>163</v>
+      </c>
+      <c r="I586">
+        <v>10037</v>
+      </c>
+      <c r="J586">
+        <v>7372</v>
+      </c>
+      <c r="K586">
+        <v>3113</v>
+      </c>
+      <c r="L586">
+        <v>876</v>
+      </c>
+      <c r="M586">
+        <v>1261</v>
+      </c>
+      <c r="N586">
+        <v>0</v>
+      </c>
+      <c r="O586">
+        <v>0</v>
+      </c>
+      <c r="P586">
+        <v>2736</v>
+      </c>
+      <c r="Q586">
+        <v>4346</v>
+      </c>
+      <c r="R586">
+        <v>245</v>
+      </c>
+      <c r="S586">
+        <v>2329</v>
+      </c>
+      <c r="T586">
+        <v>243</v>
+      </c>
+      <c r="U586">
+        <v>621</v>
+      </c>
+      <c r="V586">
+        <v>146</v>
+      </c>
+      <c r="W586">
+        <v>947</v>
+      </c>
+      <c r="X586">
+        <v>1319</v>
+      </c>
+      <c r="Y586">
+        <v>57</v>
+      </c>
+      <c r="Z586">
+        <v>261</v>
+      </c>
+      <c r="AA586">
+        <v>2647</v>
+      </c>
+      <c r="AB586">
+        <v>1460</v>
+      </c>
+      <c r="AC586">
+        <v>10031</v>
+      </c>
+      <c r="AD586">
+        <v>4906</v>
+      </c>
+      <c r="AE586">
+        <v>10024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="617">
   <si>
     <t>date</t>
   </si>
@@ -1862,6 +1862,9 @@
   </si>
   <si>
     <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
   </si>
 </sst>
 </file>
@@ -2204,7 +2207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE586"/>
+  <dimension ref="A1:AE587"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57616,6 +57619,101 @@
         <v>10024</v>
       </c>
     </row>
+    <row r="587" spans="1:31">
+      <c r="A587" t="s">
+        <v>616</v>
+      </c>
+      <c r="B587">
+        <v>446</v>
+      </c>
+      <c r="C587">
+        <v>1776</v>
+      </c>
+      <c r="D587">
+        <v>10017</v>
+      </c>
+      <c r="E587">
+        <v>1669</v>
+      </c>
+      <c r="F587">
+        <v>4447</v>
+      </c>
+      <c r="G587">
+        <v>5387</v>
+      </c>
+      <c r="H587">
+        <v>162</v>
+      </c>
+      <c r="I587">
+        <v>10032</v>
+      </c>
+      <c r="J587">
+        <v>7374</v>
+      </c>
+      <c r="K587">
+        <v>3112</v>
+      </c>
+      <c r="L587">
+        <v>876</v>
+      </c>
+      <c r="M587">
+        <v>1260</v>
+      </c>
+      <c r="N587">
+        <v>0</v>
+      </c>
+      <c r="O587">
+        <v>0</v>
+      </c>
+      <c r="P587">
+        <v>2735</v>
+      </c>
+      <c r="Q587">
+        <v>4346</v>
+      </c>
+      <c r="R587">
+        <v>245</v>
+      </c>
+      <c r="S587">
+        <v>2329</v>
+      </c>
+      <c r="T587">
+        <v>243</v>
+      </c>
+      <c r="U587">
+        <v>621</v>
+      </c>
+      <c r="V587">
+        <v>146</v>
+      </c>
+      <c r="W587">
+        <v>947</v>
+      </c>
+      <c r="X587">
+        <v>1318</v>
+      </c>
+      <c r="Y587">
+        <v>57</v>
+      </c>
+      <c r="Z587">
+        <v>261</v>
+      </c>
+      <c r="AA587">
+        <v>2648</v>
+      </c>
+      <c r="AB587">
+        <v>1459</v>
+      </c>
+      <c r="AC587">
+        <v>10029</v>
+      </c>
+      <c r="AD587">
+        <v>4907</v>
+      </c>
+      <c r="AE587">
+        <v>10022</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="618">
   <si>
     <t>date</t>
   </si>
@@ -1865,6 +1865,9 @@
   </si>
   <si>
     <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
   </si>
 </sst>
 </file>
@@ -2207,7 +2210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE587"/>
+  <dimension ref="A1:AE588"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57714,6 +57717,101 @@
         <v>10022</v>
       </c>
     </row>
+    <row r="588" spans="1:31">
+      <c r="A588" t="s">
+        <v>617</v>
+      </c>
+      <c r="B588">
+        <v>445</v>
+      </c>
+      <c r="C588">
+        <v>1776</v>
+      </c>
+      <c r="D588">
+        <v>10016</v>
+      </c>
+      <c r="E588">
+        <v>1669</v>
+      </c>
+      <c r="F588">
+        <v>4451</v>
+      </c>
+      <c r="G588">
+        <v>5388</v>
+      </c>
+      <c r="H588">
+        <v>163</v>
+      </c>
+      <c r="I588">
+        <v>10034</v>
+      </c>
+      <c r="J588">
+        <v>7376</v>
+      </c>
+      <c r="K588">
+        <v>3112</v>
+      </c>
+      <c r="L588">
+        <v>877</v>
+      </c>
+      <c r="M588">
+        <v>1261</v>
+      </c>
+      <c r="N588">
+        <v>0</v>
+      </c>
+      <c r="O588">
+        <v>0</v>
+      </c>
+      <c r="P588">
+        <v>2737</v>
+      </c>
+      <c r="Q588">
+        <v>4348</v>
+      </c>
+      <c r="R588">
+        <v>245</v>
+      </c>
+      <c r="S588">
+        <v>2328</v>
+      </c>
+      <c r="T588">
+        <v>243</v>
+      </c>
+      <c r="U588">
+        <v>0</v>
+      </c>
+      <c r="V588">
+        <v>146</v>
+      </c>
+      <c r="W588">
+        <v>947</v>
+      </c>
+      <c r="X588">
+        <v>1319</v>
+      </c>
+      <c r="Y588">
+        <v>57</v>
+      </c>
+      <c r="Z588">
+        <v>261</v>
+      </c>
+      <c r="AA588">
+        <v>2648</v>
+      </c>
+      <c r="AB588">
+        <v>1459</v>
+      </c>
+      <c r="AC588">
+        <v>10028</v>
+      </c>
+      <c r="AD588">
+        <v>4909</v>
+      </c>
+      <c r="AE588">
+        <v>10023</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="619">
   <si>
     <t>date</t>
   </si>
@@ -1868,6 +1868,9 @@
   </si>
   <si>
     <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
   </si>
 </sst>
 </file>
@@ -2210,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE588"/>
+  <dimension ref="A1:AE589"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57812,6 +57815,101 @@
         <v>10023</v>
       </c>
     </row>
+    <row r="589" spans="1:31">
+      <c r="A589" t="s">
+        <v>618</v>
+      </c>
+      <c r="B589">
+        <v>445</v>
+      </c>
+      <c r="C589">
+        <v>1776</v>
+      </c>
+      <c r="D589">
+        <v>10009</v>
+      </c>
+      <c r="E589">
+        <v>1668</v>
+      </c>
+      <c r="F589">
+        <v>4452</v>
+      </c>
+      <c r="G589">
+        <v>5388</v>
+      </c>
+      <c r="H589">
+        <v>162</v>
+      </c>
+      <c r="I589">
+        <v>10034</v>
+      </c>
+      <c r="J589">
+        <v>7377</v>
+      </c>
+      <c r="K589">
+        <v>3113</v>
+      </c>
+      <c r="L589">
+        <v>877</v>
+      </c>
+      <c r="M589">
+        <v>1259</v>
+      </c>
+      <c r="N589">
+        <v>0</v>
+      </c>
+      <c r="O589">
+        <v>0</v>
+      </c>
+      <c r="P589">
+        <v>2737</v>
+      </c>
+      <c r="Q589">
+        <v>4348</v>
+      </c>
+      <c r="R589">
+        <v>245</v>
+      </c>
+      <c r="S589">
+        <v>2328</v>
+      </c>
+      <c r="T589">
+        <v>243</v>
+      </c>
+      <c r="U589">
+        <v>0</v>
+      </c>
+      <c r="V589">
+        <v>146</v>
+      </c>
+      <c r="W589">
+        <v>947</v>
+      </c>
+      <c r="X589">
+        <v>1319</v>
+      </c>
+      <c r="Y589">
+        <v>57</v>
+      </c>
+      <c r="Z589">
+        <v>261</v>
+      </c>
+      <c r="AA589">
+        <v>2650</v>
+      </c>
+      <c r="AB589">
+        <v>1458</v>
+      </c>
+      <c r="AC589">
+        <v>10027</v>
+      </c>
+      <c r="AD589">
+        <v>4907</v>
+      </c>
+      <c r="AE589">
+        <v>10022</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="620">
   <si>
     <t>date</t>
   </si>
@@ -1871,6 +1871,9 @@
   </si>
   <si>
     <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2026-10-11</t>
   </si>
 </sst>
 </file>
@@ -2213,7 +2216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE589"/>
+  <dimension ref="A1:AE590"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -57910,6 +57913,101 @@
         <v>10022</v>
       </c>
     </row>
+    <row r="590" spans="1:31">
+      <c r="A590" t="s">
+        <v>619</v>
+      </c>
+      <c r="B590">
+        <v>444</v>
+      </c>
+      <c r="C590">
+        <v>1775</v>
+      </c>
+      <c r="D590">
+        <v>10014</v>
+      </c>
+      <c r="E590">
+        <v>1668</v>
+      </c>
+      <c r="F590">
+        <v>4453</v>
+      </c>
+      <c r="G590">
+        <v>5390</v>
+      </c>
+      <c r="H590">
+        <v>162</v>
+      </c>
+      <c r="I590">
+        <v>10033</v>
+      </c>
+      <c r="J590">
+        <v>7379</v>
+      </c>
+      <c r="K590">
+        <v>3112</v>
+      </c>
+      <c r="L590">
+        <v>878</v>
+      </c>
+      <c r="M590">
+        <v>1258</v>
+      </c>
+      <c r="N590">
+        <v>0</v>
+      </c>
+      <c r="O590">
+        <v>0</v>
+      </c>
+      <c r="P590">
+        <v>2737</v>
+      </c>
+      <c r="Q590">
+        <v>4350</v>
+      </c>
+      <c r="R590">
+        <v>245</v>
+      </c>
+      <c r="S590">
+        <v>2328</v>
+      </c>
+      <c r="T590">
+        <v>243</v>
+      </c>
+      <c r="U590">
+        <v>0</v>
+      </c>
+      <c r="V590">
+        <v>146</v>
+      </c>
+      <c r="W590">
+        <v>947</v>
+      </c>
+      <c r="X590">
+        <v>1318</v>
+      </c>
+      <c r="Y590">
+        <v>57</v>
+      </c>
+      <c r="Z590">
+        <v>261</v>
+      </c>
+      <c r="AA590">
+        <v>2649</v>
+      </c>
+      <c r="AB590">
+        <v>1456</v>
+      </c>
+      <c r="AC590">
+        <v>10026</v>
+      </c>
+      <c r="AD590">
+        <v>4908</v>
+      </c>
+      <c r="AE590">
+        <v>10020</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="621">
   <si>
     <t>date</t>
   </si>
@@ -1874,6 +1874,9 @@
   </si>
   <si>
     <t>2026-10-11</t>
+  </si>
+  <si>
+    <t>2026-10-12</t>
   </si>
 </sst>
 </file>
@@ -2216,7 +2219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE590"/>
+  <dimension ref="A1:AE591"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58008,6 +58011,101 @@
         <v>10020</v>
       </c>
     </row>
+    <row r="591" spans="1:31">
+      <c r="A591" t="s">
+        <v>620</v>
+      </c>
+      <c r="B591">
+        <v>444</v>
+      </c>
+      <c r="C591">
+        <v>1775</v>
+      </c>
+      <c r="D591">
+        <v>10006</v>
+      </c>
+      <c r="E591">
+        <v>1669</v>
+      </c>
+      <c r="F591">
+        <v>4451</v>
+      </c>
+      <c r="G591">
+        <v>5389</v>
+      </c>
+      <c r="H591">
+        <v>162</v>
+      </c>
+      <c r="I591">
+        <v>10030</v>
+      </c>
+      <c r="J591">
+        <v>7380</v>
+      </c>
+      <c r="K591">
+        <v>3114</v>
+      </c>
+      <c r="L591">
+        <v>878</v>
+      </c>
+      <c r="M591">
+        <v>1260</v>
+      </c>
+      <c r="N591">
+        <v>0</v>
+      </c>
+      <c r="O591">
+        <v>0</v>
+      </c>
+      <c r="P591">
+        <v>2736</v>
+      </c>
+      <c r="Q591">
+        <v>4352</v>
+      </c>
+      <c r="R591">
+        <v>245</v>
+      </c>
+      <c r="S591">
+        <v>2328</v>
+      </c>
+      <c r="T591">
+        <v>243</v>
+      </c>
+      <c r="U591">
+        <v>0</v>
+      </c>
+      <c r="V591">
+        <v>146</v>
+      </c>
+      <c r="W591">
+        <v>947</v>
+      </c>
+      <c r="X591">
+        <v>1317</v>
+      </c>
+      <c r="Y591">
+        <v>57</v>
+      </c>
+      <c r="Z591">
+        <v>263</v>
+      </c>
+      <c r="AA591">
+        <v>2650</v>
+      </c>
+      <c r="AB591">
+        <v>1458</v>
+      </c>
+      <c r="AC591">
+        <v>10025</v>
+      </c>
+      <c r="AD591">
+        <v>4911</v>
+      </c>
+      <c r="AE591">
+        <v>10021</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="622">
   <si>
     <t>date</t>
   </si>
@@ -1877,6 +1877,9 @@
   </si>
   <si>
     <t>2026-10-12</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
   </si>
 </sst>
 </file>
@@ -2219,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE591"/>
+  <dimension ref="A1:AE592"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58106,6 +58109,101 @@
         <v>10021</v>
       </c>
     </row>
+    <row r="592" spans="1:31">
+      <c r="A592" t="s">
+        <v>621</v>
+      </c>
+      <c r="B592">
+        <v>444</v>
+      </c>
+      <c r="C592">
+        <v>1775</v>
+      </c>
+      <c r="D592">
+        <v>10086</v>
+      </c>
+      <c r="E592">
+        <v>1669</v>
+      </c>
+      <c r="F592">
+        <v>4452</v>
+      </c>
+      <c r="G592">
+        <v>5391</v>
+      </c>
+      <c r="H592">
+        <v>162</v>
+      </c>
+      <c r="I592">
+        <v>10030</v>
+      </c>
+      <c r="J592">
+        <v>7380</v>
+      </c>
+      <c r="K592">
+        <v>3116</v>
+      </c>
+      <c r="L592">
+        <v>877</v>
+      </c>
+      <c r="M592">
+        <v>1260</v>
+      </c>
+      <c r="N592">
+        <v>0</v>
+      </c>
+      <c r="O592">
+        <v>0</v>
+      </c>
+      <c r="P592">
+        <v>2737</v>
+      </c>
+      <c r="Q592">
+        <v>4353</v>
+      </c>
+      <c r="R592">
+        <v>245</v>
+      </c>
+      <c r="S592">
+        <v>2329</v>
+      </c>
+      <c r="T592">
+        <v>243</v>
+      </c>
+      <c r="U592">
+        <v>0</v>
+      </c>
+      <c r="V592">
+        <v>146</v>
+      </c>
+      <c r="W592">
+        <v>947</v>
+      </c>
+      <c r="X592">
+        <v>1317</v>
+      </c>
+      <c r="Y592">
+        <v>57</v>
+      </c>
+      <c r="Z592">
+        <v>263</v>
+      </c>
+      <c r="AA592">
+        <v>2650</v>
+      </c>
+      <c r="AB592">
+        <v>1458</v>
+      </c>
+      <c r="AC592">
+        <v>10024</v>
+      </c>
+      <c r="AD592">
+        <v>4912</v>
+      </c>
+      <c r="AE592">
+        <v>10019</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="623">
   <si>
     <t>date</t>
   </si>
@@ -1880,6 +1880,9 @@
   </si>
   <si>
     <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>2026-10-14</t>
   </si>
 </sst>
 </file>
@@ -2222,7 +2225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE592"/>
+  <dimension ref="A1:AE593"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58204,6 +58207,101 @@
         <v>10019</v>
       </c>
     </row>
+    <row r="593" spans="1:31">
+      <c r="A593" t="s">
+        <v>622</v>
+      </c>
+      <c r="B593">
+        <v>444</v>
+      </c>
+      <c r="C593">
+        <v>1778</v>
+      </c>
+      <c r="D593">
+        <v>10062</v>
+      </c>
+      <c r="E593">
+        <v>1669</v>
+      </c>
+      <c r="F593">
+        <v>4454</v>
+      </c>
+      <c r="G593">
+        <v>5392</v>
+      </c>
+      <c r="H593">
+        <v>162</v>
+      </c>
+      <c r="I593">
+        <v>10028</v>
+      </c>
+      <c r="J593">
+        <v>7378</v>
+      </c>
+      <c r="K593">
+        <v>3115</v>
+      </c>
+      <c r="L593">
+        <v>877</v>
+      </c>
+      <c r="M593">
+        <v>1260</v>
+      </c>
+      <c r="N593">
+        <v>0</v>
+      </c>
+      <c r="O593">
+        <v>0</v>
+      </c>
+      <c r="P593">
+        <v>2738</v>
+      </c>
+      <c r="Q593">
+        <v>4354</v>
+      </c>
+      <c r="R593">
+        <v>245</v>
+      </c>
+      <c r="S593">
+        <v>2330</v>
+      </c>
+      <c r="T593">
+        <v>242</v>
+      </c>
+      <c r="U593">
+        <v>0</v>
+      </c>
+      <c r="V593">
+        <v>146</v>
+      </c>
+      <c r="W593">
+        <v>946</v>
+      </c>
+      <c r="X593">
+        <v>1317</v>
+      </c>
+      <c r="Y593">
+        <v>57</v>
+      </c>
+      <c r="Z593">
+        <v>264</v>
+      </c>
+      <c r="AA593">
+        <v>2650</v>
+      </c>
+      <c r="AB593">
+        <v>1458</v>
+      </c>
+      <c r="AC593">
+        <v>10019</v>
+      </c>
+      <c r="AD593">
+        <v>4912</v>
+      </c>
+      <c r="AE593">
+        <v>10019</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="624">
   <si>
     <t>date</t>
   </si>
@@ -1883,6 +1883,9 @@
   </si>
   <si>
     <t>2026-10-14</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
   </si>
 </sst>
 </file>
@@ -2225,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE593"/>
+  <dimension ref="A1:AE594"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58302,6 +58305,101 @@
         <v>10019</v>
       </c>
     </row>
+    <row r="594" spans="1:31">
+      <c r="A594" t="s">
+        <v>623</v>
+      </c>
+      <c r="B594">
+        <v>443</v>
+      </c>
+      <c r="C594">
+        <v>1778</v>
+      </c>
+      <c r="D594">
+        <v>10065</v>
+      </c>
+      <c r="E594">
+        <v>1669</v>
+      </c>
+      <c r="F594">
+        <v>4454</v>
+      </c>
+      <c r="G594">
+        <v>5395</v>
+      </c>
+      <c r="H594">
+        <v>161</v>
+      </c>
+      <c r="I594">
+        <v>10030</v>
+      </c>
+      <c r="J594">
+        <v>7381</v>
+      </c>
+      <c r="K594">
+        <v>3115</v>
+      </c>
+      <c r="L594">
+        <v>877</v>
+      </c>
+      <c r="M594">
+        <v>1262</v>
+      </c>
+      <c r="N594">
+        <v>0</v>
+      </c>
+      <c r="O594">
+        <v>0</v>
+      </c>
+      <c r="P594">
+        <v>2740</v>
+      </c>
+      <c r="Q594">
+        <v>4354</v>
+      </c>
+      <c r="R594">
+        <v>245</v>
+      </c>
+      <c r="S594">
+        <v>2330</v>
+      </c>
+      <c r="T594">
+        <v>242</v>
+      </c>
+      <c r="U594">
+        <v>0</v>
+      </c>
+      <c r="V594">
+        <v>146</v>
+      </c>
+      <c r="W594">
+        <v>946</v>
+      </c>
+      <c r="X594">
+        <v>1317</v>
+      </c>
+      <c r="Y594">
+        <v>57</v>
+      </c>
+      <c r="Z594">
+        <v>264</v>
+      </c>
+      <c r="AA594">
+        <v>2653</v>
+      </c>
+      <c r="AB594">
+        <v>1459</v>
+      </c>
+      <c r="AC594">
+        <v>10019</v>
+      </c>
+      <c r="AD594">
+        <v>4913</v>
+      </c>
+      <c r="AE594">
+        <v>10019</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="625">
   <si>
     <t>date</t>
   </si>
@@ -1886,6 +1886,9 @@
   </si>
   <si>
     <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
   </si>
 </sst>
 </file>
@@ -2228,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE594"/>
+  <dimension ref="A1:AE595"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58400,6 +58403,101 @@
         <v>10019</v>
       </c>
     </row>
+    <row r="595" spans="1:31">
+      <c r="A595" t="s">
+        <v>624</v>
+      </c>
+      <c r="B595">
+        <v>443</v>
+      </c>
+      <c r="C595">
+        <v>1778</v>
+      </c>
+      <c r="D595">
+        <v>10064</v>
+      </c>
+      <c r="E595">
+        <v>1670</v>
+      </c>
+      <c r="F595">
+        <v>4455</v>
+      </c>
+      <c r="G595">
+        <v>5402</v>
+      </c>
+      <c r="H595">
+        <v>162</v>
+      </c>
+      <c r="I595">
+        <v>10028</v>
+      </c>
+      <c r="J595">
+        <v>7384</v>
+      </c>
+      <c r="K595">
+        <v>3115</v>
+      </c>
+      <c r="L595">
+        <v>877</v>
+      </c>
+      <c r="M595">
+        <v>1263</v>
+      </c>
+      <c r="N595">
+        <v>0</v>
+      </c>
+      <c r="O595">
+        <v>0</v>
+      </c>
+      <c r="P595">
+        <v>2741</v>
+      </c>
+      <c r="Q595">
+        <v>4354</v>
+      </c>
+      <c r="R595">
+        <v>245</v>
+      </c>
+      <c r="S595">
+        <v>2330</v>
+      </c>
+      <c r="T595">
+        <v>242</v>
+      </c>
+      <c r="U595">
+        <v>0</v>
+      </c>
+      <c r="V595">
+        <v>146</v>
+      </c>
+      <c r="W595">
+        <v>946</v>
+      </c>
+      <c r="X595">
+        <v>1319</v>
+      </c>
+      <c r="Y595">
+        <v>57</v>
+      </c>
+      <c r="Z595">
+        <v>264</v>
+      </c>
+      <c r="AA595">
+        <v>2651</v>
+      </c>
+      <c r="AB595">
+        <v>1458</v>
+      </c>
+      <c r="AC595">
+        <v>10020</v>
+      </c>
+      <c r="AD595">
+        <v>4916</v>
+      </c>
+      <c r="AE595">
+        <v>10016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="626">
   <si>
     <t>date</t>
   </si>
@@ -1889,6 +1889,9 @@
   </si>
   <si>
     <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-10-17</t>
   </si>
 </sst>
 </file>
@@ -2231,7 +2234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE595"/>
+  <dimension ref="A1:AE596"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58498,6 +58501,101 @@
         <v>10016</v>
       </c>
     </row>
+    <row r="596" spans="1:31">
+      <c r="A596" t="s">
+        <v>625</v>
+      </c>
+      <c r="B596">
+        <v>444</v>
+      </c>
+      <c r="C596">
+        <v>1779</v>
+      </c>
+      <c r="D596">
+        <v>10072</v>
+      </c>
+      <c r="E596">
+        <v>1670</v>
+      </c>
+      <c r="F596">
+        <v>4455</v>
+      </c>
+      <c r="G596">
+        <v>5402</v>
+      </c>
+      <c r="H596">
+        <v>162</v>
+      </c>
+      <c r="I596">
+        <v>10027</v>
+      </c>
+      <c r="J596">
+        <v>7384</v>
+      </c>
+      <c r="K596">
+        <v>3115</v>
+      </c>
+      <c r="L596">
+        <v>877</v>
+      </c>
+      <c r="M596">
+        <v>1263</v>
+      </c>
+      <c r="N596">
+        <v>0</v>
+      </c>
+      <c r="O596">
+        <v>0</v>
+      </c>
+      <c r="P596">
+        <v>2742</v>
+      </c>
+      <c r="Q596">
+        <v>4354</v>
+      </c>
+      <c r="R596">
+        <v>245</v>
+      </c>
+      <c r="S596">
+        <v>2330</v>
+      </c>
+      <c r="T596">
+        <v>243</v>
+      </c>
+      <c r="U596">
+        <v>0</v>
+      </c>
+      <c r="V596">
+        <v>147</v>
+      </c>
+      <c r="W596">
+        <v>947</v>
+      </c>
+      <c r="X596">
+        <v>1317</v>
+      </c>
+      <c r="Y596">
+        <v>57</v>
+      </c>
+      <c r="Z596">
+        <v>264</v>
+      </c>
+      <c r="AA596">
+        <v>2651</v>
+      </c>
+      <c r="AB596">
+        <v>1458</v>
+      </c>
+      <c r="AC596">
+        <v>10019</v>
+      </c>
+      <c r="AD596">
+        <v>4914</v>
+      </c>
+      <c r="AE596">
+        <v>10017</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="627">
   <si>
     <t>date</t>
   </si>
@@ -1892,6 +1892,9 @@
   </si>
   <si>
     <t>2026-10-17</t>
+  </si>
+  <si>
+    <t>2026-10-18</t>
   </si>
 </sst>
 </file>
@@ -2234,7 +2237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE596"/>
+  <dimension ref="A1:AE597"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58596,6 +58599,101 @@
         <v>10017</v>
       </c>
     </row>
+    <row r="597" spans="1:31">
+      <c r="A597" t="s">
+        <v>626</v>
+      </c>
+      <c r="B597">
+        <v>443</v>
+      </c>
+      <c r="C597">
+        <v>1776</v>
+      </c>
+      <c r="D597">
+        <v>10080</v>
+      </c>
+      <c r="E597">
+        <v>1667</v>
+      </c>
+      <c r="F597">
+        <v>4444</v>
+      </c>
+      <c r="G597">
+        <v>5354</v>
+      </c>
+      <c r="H597">
+        <v>162</v>
+      </c>
+      <c r="I597">
+        <v>10049</v>
+      </c>
+      <c r="J597">
+        <v>7380</v>
+      </c>
+      <c r="K597">
+        <v>3110</v>
+      </c>
+      <c r="L597">
+        <v>870</v>
+      </c>
+      <c r="M597">
+        <v>1251</v>
+      </c>
+      <c r="N597">
+        <v>0</v>
+      </c>
+      <c r="O597">
+        <v>0</v>
+      </c>
+      <c r="P597">
+        <v>2737</v>
+      </c>
+      <c r="Q597">
+        <v>4337</v>
+      </c>
+      <c r="R597">
+        <v>245</v>
+      </c>
+      <c r="S597">
+        <v>2326</v>
+      </c>
+      <c r="T597">
+        <v>243</v>
+      </c>
+      <c r="U597">
+        <v>0</v>
+      </c>
+      <c r="V597">
+        <v>147</v>
+      </c>
+      <c r="W597">
+        <v>947</v>
+      </c>
+      <c r="X597">
+        <v>1317</v>
+      </c>
+      <c r="Y597">
+        <v>57</v>
+      </c>
+      <c r="Z597">
+        <v>264</v>
+      </c>
+      <c r="AA597">
+        <v>2647</v>
+      </c>
+      <c r="AB597">
+        <v>1445</v>
+      </c>
+      <c r="AC597">
+        <v>10082</v>
+      </c>
+      <c r="AD597">
+        <v>4903</v>
+      </c>
+      <c r="AE597">
+        <v>10094</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="628">
   <si>
     <t>date</t>
   </si>
@@ -1895,6 +1895,9 @@
   </si>
   <si>
     <t>2026-10-18</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
   </si>
 </sst>
 </file>
@@ -2237,7 +2240,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE597"/>
+  <dimension ref="A1:AE598"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58694,6 +58697,101 @@
         <v>10094</v>
       </c>
     </row>
+    <row r="598" spans="1:31">
+      <c r="A598" t="s">
+        <v>627</v>
+      </c>
+      <c r="B598">
+        <v>444</v>
+      </c>
+      <c r="C598">
+        <v>1775</v>
+      </c>
+      <c r="D598">
+        <v>10031</v>
+      </c>
+      <c r="E598">
+        <v>1666</v>
+      </c>
+      <c r="F598">
+        <v>4451</v>
+      </c>
+      <c r="G598">
+        <v>5391</v>
+      </c>
+      <c r="H598">
+        <v>162</v>
+      </c>
+      <c r="I598">
+        <v>10091</v>
+      </c>
+      <c r="J598">
+        <v>7388</v>
+      </c>
+      <c r="K598">
+        <v>3108</v>
+      </c>
+      <c r="L598">
+        <v>878</v>
+      </c>
+      <c r="M598">
+        <v>1259</v>
+      </c>
+      <c r="N598">
+        <v>0</v>
+      </c>
+      <c r="O598">
+        <v>0</v>
+      </c>
+      <c r="P598">
+        <v>2739</v>
+      </c>
+      <c r="Q598">
+        <v>4350</v>
+      </c>
+      <c r="R598">
+        <v>245</v>
+      </c>
+      <c r="S598">
+        <v>2328</v>
+      </c>
+      <c r="T598">
+        <v>244</v>
+      </c>
+      <c r="U598">
+        <v>0</v>
+      </c>
+      <c r="V598">
+        <v>147</v>
+      </c>
+      <c r="W598">
+        <v>947</v>
+      </c>
+      <c r="X598">
+        <v>1317</v>
+      </c>
+      <c r="Y598">
+        <v>57</v>
+      </c>
+      <c r="Z598">
+        <v>264</v>
+      </c>
+      <c r="AA598">
+        <v>2651</v>
+      </c>
+      <c r="AB598">
+        <v>1455</v>
+      </c>
+      <c r="AC598">
+        <v>10003</v>
+      </c>
+      <c r="AD598">
+        <v>4918</v>
+      </c>
+      <c r="AE598">
+        <v>10006</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="629">
   <si>
     <t>date</t>
   </si>
@@ -1898,6 +1898,9 @@
   </si>
   <si>
     <t>2026-10-19</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
   </si>
 </sst>
 </file>
@@ -2240,7 +2243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE598"/>
+  <dimension ref="A1:AE599"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58792,6 +58795,101 @@
         <v>10006</v>
       </c>
     </row>
+    <row r="599" spans="1:31">
+      <c r="A599" t="s">
+        <v>628</v>
+      </c>
+      <c r="B599">
+        <v>445</v>
+      </c>
+      <c r="C599">
+        <v>1776</v>
+      </c>
+      <c r="D599">
+        <v>10043</v>
+      </c>
+      <c r="E599">
+        <v>1665</v>
+      </c>
+      <c r="F599">
+        <v>4450</v>
+      </c>
+      <c r="G599">
+        <v>5403</v>
+      </c>
+      <c r="H599">
+        <v>162</v>
+      </c>
+      <c r="I599">
+        <v>10008</v>
+      </c>
+      <c r="J599">
+        <v>7393</v>
+      </c>
+      <c r="K599">
+        <v>3107</v>
+      </c>
+      <c r="L599">
+        <v>878</v>
+      </c>
+      <c r="M599">
+        <v>1263</v>
+      </c>
+      <c r="N599">
+        <v>0</v>
+      </c>
+      <c r="O599">
+        <v>0</v>
+      </c>
+      <c r="P599">
+        <v>2740</v>
+      </c>
+      <c r="Q599">
+        <v>4353</v>
+      </c>
+      <c r="R599">
+        <v>245</v>
+      </c>
+      <c r="S599">
+        <v>2324</v>
+      </c>
+      <c r="T599">
+        <v>243</v>
+      </c>
+      <c r="U599">
+        <v>0</v>
+      </c>
+      <c r="V599">
+        <v>147</v>
+      </c>
+      <c r="W599">
+        <v>947</v>
+      </c>
+      <c r="X599">
+        <v>1317</v>
+      </c>
+      <c r="Y599">
+        <v>57</v>
+      </c>
+      <c r="Z599">
+        <v>264</v>
+      </c>
+      <c r="AA599">
+        <v>2649</v>
+      </c>
+      <c r="AB599">
+        <v>1457</v>
+      </c>
+      <c r="AC599">
+        <v>10007</v>
+      </c>
+      <c r="AD599">
+        <v>4920</v>
+      </c>
+      <c r="AE599">
+        <v>10010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="630">
   <si>
     <t>date</t>
   </si>
@@ -1901,6 +1901,9 @@
   </si>
   <si>
     <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
   </si>
 </sst>
 </file>
@@ -2243,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE599"/>
+  <dimension ref="A1:AE600"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58890,6 +58893,101 @@
         <v>10010</v>
       </c>
     </row>
+    <row r="600" spans="1:31">
+      <c r="A600" t="s">
+        <v>629</v>
+      </c>
+      <c r="B600">
+        <v>445</v>
+      </c>
+      <c r="C600">
+        <v>1776</v>
+      </c>
+      <c r="D600">
+        <v>10042</v>
+      </c>
+      <c r="E600">
+        <v>1665</v>
+      </c>
+      <c r="F600">
+        <v>4455</v>
+      </c>
+      <c r="G600">
+        <v>5410</v>
+      </c>
+      <c r="H600">
+        <v>162</v>
+      </c>
+      <c r="I600">
+        <v>10011</v>
+      </c>
+      <c r="J600">
+        <v>7394</v>
+      </c>
+      <c r="K600">
+        <v>3108</v>
+      </c>
+      <c r="L600">
+        <v>879</v>
+      </c>
+      <c r="M600">
+        <v>1263</v>
+      </c>
+      <c r="N600">
+        <v>0</v>
+      </c>
+      <c r="O600">
+        <v>0</v>
+      </c>
+      <c r="P600">
+        <v>2741</v>
+      </c>
+      <c r="Q600">
+        <v>4354</v>
+      </c>
+      <c r="R600">
+        <v>245</v>
+      </c>
+      <c r="S600">
+        <v>2326</v>
+      </c>
+      <c r="T600">
+        <v>244</v>
+      </c>
+      <c r="U600">
+        <v>0</v>
+      </c>
+      <c r="V600">
+        <v>147</v>
+      </c>
+      <c r="W600">
+        <v>947</v>
+      </c>
+      <c r="X600">
+        <v>1318</v>
+      </c>
+      <c r="Y600">
+        <v>57</v>
+      </c>
+      <c r="Z600">
+        <v>266</v>
+      </c>
+      <c r="AA600">
+        <v>2649</v>
+      </c>
+      <c r="AB600">
+        <v>1459</v>
+      </c>
+      <c r="AC600">
+        <v>10006</v>
+      </c>
+      <c r="AD600">
+        <v>4917</v>
+      </c>
+      <c r="AE600">
+        <v>10011</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="631">
   <si>
     <t>date</t>
   </si>
@@ -1904,6 +1904,9 @@
   </si>
   <si>
     <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
   </si>
 </sst>
 </file>
@@ -2246,7 +2249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE600"/>
+  <dimension ref="A1:AE601"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -58988,6 +58991,101 @@
         <v>10011</v>
       </c>
     </row>
+    <row r="601" spans="1:31">
+      <c r="A601" t="s">
+        <v>630</v>
+      </c>
+      <c r="B601">
+        <v>445</v>
+      </c>
+      <c r="C601">
+        <v>1777</v>
+      </c>
+      <c r="D601">
+        <v>10037</v>
+      </c>
+      <c r="E601">
+        <v>1666</v>
+      </c>
+      <c r="F601">
+        <v>4455</v>
+      </c>
+      <c r="G601">
+        <v>5414</v>
+      </c>
+      <c r="H601">
+        <v>162</v>
+      </c>
+      <c r="I601">
+        <v>10013</v>
+      </c>
+      <c r="J601">
+        <v>7395</v>
+      </c>
+      <c r="K601">
+        <v>3110</v>
+      </c>
+      <c r="L601">
+        <v>881</v>
+      </c>
+      <c r="M601">
+        <v>1264</v>
+      </c>
+      <c r="N601">
+        <v>0</v>
+      </c>
+      <c r="O601">
+        <v>0</v>
+      </c>
+      <c r="P601">
+        <v>2745</v>
+      </c>
+      <c r="Q601">
+        <v>4354</v>
+      </c>
+      <c r="R601">
+        <v>245</v>
+      </c>
+      <c r="S601">
+        <v>2327</v>
+      </c>
+      <c r="T601">
+        <v>244</v>
+      </c>
+      <c r="U601">
+        <v>0</v>
+      </c>
+      <c r="V601">
+        <v>147</v>
+      </c>
+      <c r="W601">
+        <v>947</v>
+      </c>
+      <c r="X601">
+        <v>1318</v>
+      </c>
+      <c r="Y601">
+        <v>57</v>
+      </c>
+      <c r="Z601">
+        <v>265</v>
+      </c>
+      <c r="AA601">
+        <v>2651</v>
+      </c>
+      <c r="AB601">
+        <v>1458</v>
+      </c>
+      <c r="AC601">
+        <v>10003</v>
+      </c>
+      <c r="AD601">
+        <v>4919</v>
+      </c>
+      <c r="AE601">
+        <v>10010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="632">
   <si>
     <t>date</t>
   </si>
@@ -1907,6 +1907,9 @@
   </si>
   <si>
     <t>2026-10-22</t>
+  </si>
+  <si>
+    <t>2026-10-23</t>
   </si>
 </sst>
 </file>
@@ -2249,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE601"/>
+  <dimension ref="A1:AE602"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -59086,6 +59089,101 @@
         <v>10010</v>
       </c>
     </row>
+    <row r="602" spans="1:31">
+      <c r="A602" t="s">
+        <v>631</v>
+      </c>
+      <c r="B602">
+        <v>447</v>
+      </c>
+      <c r="C602">
+        <v>1776</v>
+      </c>
+      <c r="D602">
+        <v>10029</v>
+      </c>
+      <c r="E602">
+        <v>1666</v>
+      </c>
+      <c r="F602">
+        <v>4458</v>
+      </c>
+      <c r="G602">
+        <v>5419</v>
+      </c>
+      <c r="H602">
+        <v>161</v>
+      </c>
+      <c r="I602">
+        <v>10014</v>
+      </c>
+      <c r="J602">
+        <v>7392</v>
+      </c>
+      <c r="K602">
+        <v>3110</v>
+      </c>
+      <c r="L602">
+        <v>881</v>
+      </c>
+      <c r="M602">
+        <v>1264</v>
+      </c>
+      <c r="N602">
+        <v>0</v>
+      </c>
+      <c r="O602">
+        <v>0</v>
+      </c>
+      <c r="P602">
+        <v>2745</v>
+      </c>
+      <c r="Q602">
+        <v>4357</v>
+      </c>
+      <c r="R602">
+        <v>244</v>
+      </c>
+      <c r="S602">
+        <v>2327</v>
+      </c>
+      <c r="T602">
+        <v>244</v>
+      </c>
+      <c r="U602">
+        <v>0</v>
+      </c>
+      <c r="V602">
+        <v>147</v>
+      </c>
+      <c r="W602">
+        <v>947</v>
+      </c>
+      <c r="X602">
+        <v>1315</v>
+      </c>
+      <c r="Y602">
+        <v>57</v>
+      </c>
+      <c r="Z602">
+        <v>265</v>
+      </c>
+      <c r="AA602">
+        <v>2650</v>
+      </c>
+      <c r="AB602">
+        <v>1458</v>
+      </c>
+      <c r="AC602">
+        <v>10004</v>
+      </c>
+      <c r="AD602">
+        <v>4919</v>
+      </c>
+      <c r="AE602">
+        <v>10011</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
   <si>
     <t>date</t>
   </si>
@@ -1910,6 +1910,9 @@
   </si>
   <si>
     <t>2026-10-23</t>
+  </si>
+  <si>
+    <t>2026-10-24</t>
   </si>
 </sst>
 </file>
@@ -2252,7 +2255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE602"/>
+  <dimension ref="A1:AE603"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -59184,6 +59187,101 @@
         <v>10011</v>
       </c>
     </row>
+    <row r="603" spans="1:31">
+      <c r="A603" t="s">
+        <v>632</v>
+      </c>
+      <c r="B603">
+        <v>448</v>
+      </c>
+      <c r="C603">
+        <v>1778</v>
+      </c>
+      <c r="D603">
+        <v>10024</v>
+      </c>
+      <c r="E603">
+        <v>1666</v>
+      </c>
+      <c r="F603">
+        <v>4458</v>
+      </c>
+      <c r="G603">
+        <v>5424</v>
+      </c>
+      <c r="H603">
+        <v>160</v>
+      </c>
+      <c r="I603">
+        <v>10015</v>
+      </c>
+      <c r="J603">
+        <v>7394</v>
+      </c>
+      <c r="K603">
+        <v>3111</v>
+      </c>
+      <c r="L603">
+        <v>881</v>
+      </c>
+      <c r="M603">
+        <v>1265</v>
+      </c>
+      <c r="N603">
+        <v>0</v>
+      </c>
+      <c r="O603">
+        <v>0</v>
+      </c>
+      <c r="P603">
+        <v>2744</v>
+      </c>
+      <c r="Q603">
+        <v>4359</v>
+      </c>
+      <c r="R603">
+        <v>244</v>
+      </c>
+      <c r="S603">
+        <v>2327</v>
+      </c>
+      <c r="T603">
+        <v>244</v>
+      </c>
+      <c r="U603">
+        <v>0</v>
+      </c>
+      <c r="V603">
+        <v>147</v>
+      </c>
+      <c r="W603">
+        <v>948</v>
+      </c>
+      <c r="X603">
+        <v>1315</v>
+      </c>
+      <c r="Y603">
+        <v>57</v>
+      </c>
+      <c r="Z603">
+        <v>265</v>
+      </c>
+      <c r="AA603">
+        <v>2649</v>
+      </c>
+      <c r="AB603">
+        <v>1458</v>
+      </c>
+      <c r="AC603">
+        <v>10005</v>
+      </c>
+      <c r="AD603">
+        <v>4923</v>
+      </c>
+      <c r="AE603">
+        <v>10012</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="634">
   <si>
     <t>date</t>
   </si>
@@ -1913,6 +1913,9 @@
   </si>
   <si>
     <t>2026-10-24</t>
+  </si>
+  <si>
+    <t>2026-10-25</t>
   </si>
 </sst>
 </file>
@@ -2255,7 +2258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE603"/>
+  <dimension ref="A1:AE604"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -59282,6 +59285,101 @@
         <v>10012</v>
       </c>
     </row>
+    <row r="604" spans="1:31">
+      <c r="A604" t="s">
+        <v>633</v>
+      </c>
+      <c r="B604">
+        <v>448</v>
+      </c>
+      <c r="C604">
+        <v>1778</v>
+      </c>
+      <c r="D604">
+        <v>10014</v>
+      </c>
+      <c r="E604">
+        <v>1667</v>
+      </c>
+      <c r="F604">
+        <v>4460</v>
+      </c>
+      <c r="G604">
+        <v>5424</v>
+      </c>
+      <c r="H604">
+        <v>160</v>
+      </c>
+      <c r="I604">
+        <v>10014</v>
+      </c>
+      <c r="J604">
+        <v>7390</v>
+      </c>
+      <c r="K604">
+        <v>3110</v>
+      </c>
+      <c r="L604">
+        <v>883</v>
+      </c>
+      <c r="M604">
+        <v>1265</v>
+      </c>
+      <c r="N604">
+        <v>0</v>
+      </c>
+      <c r="O604">
+        <v>0</v>
+      </c>
+      <c r="P604">
+        <v>2743</v>
+      </c>
+      <c r="Q604">
+        <v>4358</v>
+      </c>
+      <c r="R604">
+        <v>244</v>
+      </c>
+      <c r="S604">
+        <v>2327</v>
+      </c>
+      <c r="T604">
+        <v>246</v>
+      </c>
+      <c r="U604">
+        <v>0</v>
+      </c>
+      <c r="V604">
+        <v>147</v>
+      </c>
+      <c r="W604">
+        <v>948</v>
+      </c>
+      <c r="X604">
+        <v>1315</v>
+      </c>
+      <c r="Y604">
+        <v>57</v>
+      </c>
+      <c r="Z604">
+        <v>265</v>
+      </c>
+      <c r="AA604">
+        <v>2649</v>
+      </c>
+      <c r="AB604">
+        <v>1458</v>
+      </c>
+      <c r="AC604">
+        <v>10006</v>
+      </c>
+      <c r="AD604">
+        <v>4922</v>
+      </c>
+      <c r="AE604">
+        <v>10011</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="635">
   <si>
     <t>date</t>
   </si>
@@ -1916,6 +1916,9 @@
   </si>
   <si>
     <t>2026-10-25</t>
+  </si>
+  <si>
+    <t>2026-10-26</t>
   </si>
 </sst>
 </file>
@@ -2258,7 +2261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE604"/>
+  <dimension ref="A1:AE605"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -59380,6 +59383,101 @@
         <v>10011</v>
       </c>
     </row>
+    <row r="605" spans="1:31">
+      <c r="A605" t="s">
+        <v>634</v>
+      </c>
+      <c r="B605">
+        <v>445</v>
+      </c>
+      <c r="C605">
+        <v>1778</v>
+      </c>
+      <c r="D605">
+        <v>10011</v>
+      </c>
+      <c r="E605">
+        <v>1667</v>
+      </c>
+      <c r="F605">
+        <v>4461</v>
+      </c>
+      <c r="G605">
+        <v>5425</v>
+      </c>
+      <c r="H605">
+        <v>160</v>
+      </c>
+      <c r="I605">
+        <v>10014</v>
+      </c>
+      <c r="J605">
+        <v>7393</v>
+      </c>
+      <c r="K605">
+        <v>3111</v>
+      </c>
+      <c r="L605">
+        <v>883</v>
+      </c>
+      <c r="M605">
+        <v>1265</v>
+      </c>
+      <c r="N605">
+        <v>0</v>
+      </c>
+      <c r="O605">
+        <v>0</v>
+      </c>
+      <c r="P605">
+        <v>2743</v>
+      </c>
+      <c r="Q605">
+        <v>4358</v>
+      </c>
+      <c r="R605">
+        <v>243</v>
+      </c>
+      <c r="S605">
+        <v>2326</v>
+      </c>
+      <c r="T605">
+        <v>249</v>
+      </c>
+      <c r="U605">
+        <v>0</v>
+      </c>
+      <c r="V605">
+        <v>147</v>
+      </c>
+      <c r="W605">
+        <v>948</v>
+      </c>
+      <c r="X605">
+        <v>1315</v>
+      </c>
+      <c r="Y605">
+        <v>57</v>
+      </c>
+      <c r="Z605">
+        <v>265</v>
+      </c>
+      <c r="AA605">
+        <v>2649</v>
+      </c>
+      <c r="AB605">
+        <v>1458</v>
+      </c>
+      <c r="AC605">
+        <v>10004</v>
+      </c>
+      <c r="AD605">
+        <v>4920</v>
+      </c>
+      <c r="AE605">
+        <v>10009</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="636">
   <si>
     <t>date</t>
   </si>
@@ -1919,6 +1919,9 @@
   </si>
   <si>
     <t>2026-10-26</t>
+  </si>
+  <si>
+    <t>2026-10-27</t>
   </si>
 </sst>
 </file>
@@ -2261,7 +2264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE605"/>
+  <dimension ref="A1:AE606"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -59478,6 +59481,101 @@
         <v>10009</v>
       </c>
     </row>
+    <row r="606" spans="1:31">
+      <c r="A606" t="s">
+        <v>635</v>
+      </c>
+      <c r="B606">
+        <v>446</v>
+      </c>
+      <c r="C606">
+        <v>1779</v>
+      </c>
+      <c r="D606">
+        <v>10010</v>
+      </c>
+      <c r="E606">
+        <v>1666</v>
+      </c>
+      <c r="F606">
+        <v>4460</v>
+      </c>
+      <c r="G606">
+        <v>5438</v>
+      </c>
+      <c r="H606">
+        <v>160</v>
+      </c>
+      <c r="I606">
+        <v>10016</v>
+      </c>
+      <c r="J606">
+        <v>7392</v>
+      </c>
+      <c r="K606">
+        <v>3113</v>
+      </c>
+      <c r="L606">
+        <v>884</v>
+      </c>
+      <c r="M606">
+        <v>1266</v>
+      </c>
+      <c r="N606">
+        <v>0</v>
+      </c>
+      <c r="O606">
+        <v>0</v>
+      </c>
+      <c r="P606">
+        <v>2744</v>
+      </c>
+      <c r="Q606">
+        <v>4357</v>
+      </c>
+      <c r="R606">
+        <v>243</v>
+      </c>
+      <c r="S606">
+        <v>2327</v>
+      </c>
+      <c r="T606">
+        <v>249</v>
+      </c>
+      <c r="U606">
+        <v>0</v>
+      </c>
+      <c r="V606">
+        <v>147</v>
+      </c>
+      <c r="W606">
+        <v>947</v>
+      </c>
+      <c r="X606">
+        <v>1316</v>
+      </c>
+      <c r="Y606">
+        <v>57</v>
+      </c>
+      <c r="Z606">
+        <v>265</v>
+      </c>
+      <c r="AA606">
+        <v>2649</v>
+      </c>
+      <c r="AB606">
+        <v>1460</v>
+      </c>
+      <c r="AC606">
+        <v>10007</v>
+      </c>
+      <c r="AD606">
+        <v>4920</v>
+      </c>
+      <c r="AE606">
+        <v>10009</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="637">
   <si>
     <t>date</t>
   </si>
@@ -1922,6 +1922,9 @@
   </si>
   <si>
     <t>2026-10-27</t>
+  </si>
+  <si>
+    <t>2026-10-28</t>
   </si>
 </sst>
 </file>
@@ -2264,7 +2267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE606"/>
+  <dimension ref="A1:AE607"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -59576,6 +59579,101 @@
         <v>10009</v>
       </c>
     </row>
+    <row r="607" spans="1:31">
+      <c r="A607" t="s">
+        <v>636</v>
+      </c>
+      <c r="B607">
+        <v>447</v>
+      </c>
+      <c r="C607">
+        <v>1779</v>
+      </c>
+      <c r="D607">
+        <v>10026</v>
+      </c>
+      <c r="E607">
+        <v>1666</v>
+      </c>
+      <c r="F607">
+        <v>4460</v>
+      </c>
+      <c r="G607">
+        <v>5442</v>
+      </c>
+      <c r="H607">
+        <v>160</v>
+      </c>
+      <c r="I607">
+        <v>10020</v>
+      </c>
+      <c r="J607">
+        <v>7392</v>
+      </c>
+      <c r="K607">
+        <v>3113</v>
+      </c>
+      <c r="L607">
+        <v>885</v>
+      </c>
+      <c r="M607">
+        <v>1267</v>
+      </c>
+      <c r="N607">
+        <v>0</v>
+      </c>
+      <c r="O607">
+        <v>0</v>
+      </c>
+      <c r="P607">
+        <v>2744</v>
+      </c>
+      <c r="Q607">
+        <v>4357</v>
+      </c>
+      <c r="R607">
+        <v>243</v>
+      </c>
+      <c r="S607">
+        <v>2328</v>
+      </c>
+      <c r="T607">
+        <v>250</v>
+      </c>
+      <c r="U607">
+        <v>0</v>
+      </c>
+      <c r="V607">
+        <v>147</v>
+      </c>
+      <c r="W607">
+        <v>947</v>
+      </c>
+      <c r="X607">
+        <v>1316</v>
+      </c>
+      <c r="Y607">
+        <v>57</v>
+      </c>
+      <c r="Z607">
+        <v>265</v>
+      </c>
+      <c r="AA607">
+        <v>2647</v>
+      </c>
+      <c r="AB607">
+        <v>1459</v>
+      </c>
+      <c r="AC607">
+        <v>10002</v>
+      </c>
+      <c r="AD607">
+        <v>4920</v>
+      </c>
+      <c r="AE607">
+        <v>10002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="638">
   <si>
     <t>date</t>
   </si>
@@ -1925,6 +1925,9 @@
   </si>
   <si>
     <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
   </si>
 </sst>
 </file>
@@ -2267,7 +2270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE607"/>
+  <dimension ref="A1:AE608"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -59674,6 +59677,101 @@
         <v>10002</v>
       </c>
     </row>
+    <row r="608" spans="1:31">
+      <c r="A608" t="s">
+        <v>637</v>
+      </c>
+      <c r="B608">
+        <v>447</v>
+      </c>
+      <c r="C608">
+        <v>1779</v>
+      </c>
+      <c r="D608">
+        <v>10030</v>
+      </c>
+      <c r="E608">
+        <v>1667</v>
+      </c>
+      <c r="F608">
+        <v>4461</v>
+      </c>
+      <c r="G608">
+        <v>5446</v>
+      </c>
+      <c r="H608">
+        <v>160</v>
+      </c>
+      <c r="I608">
+        <v>10022</v>
+      </c>
+      <c r="J608">
+        <v>7394</v>
+      </c>
+      <c r="K608">
+        <v>3113</v>
+      </c>
+      <c r="L608">
+        <v>884</v>
+      </c>
+      <c r="M608">
+        <v>1269</v>
+      </c>
+      <c r="N608">
+        <v>0</v>
+      </c>
+      <c r="O608">
+        <v>0</v>
+      </c>
+      <c r="P608">
+        <v>2745</v>
+      </c>
+      <c r="Q608">
+        <v>4356</v>
+      </c>
+      <c r="R608">
+        <v>243</v>
+      </c>
+      <c r="S608">
+        <v>2328</v>
+      </c>
+      <c r="T608">
+        <v>250</v>
+      </c>
+      <c r="U608">
+        <v>0</v>
+      </c>
+      <c r="V608">
+        <v>147</v>
+      </c>
+      <c r="W608">
+        <v>947</v>
+      </c>
+      <c r="X608">
+        <v>1316</v>
+      </c>
+      <c r="Y608">
+        <v>57</v>
+      </c>
+      <c r="Z608">
+        <v>265</v>
+      </c>
+      <c r="AA608">
+        <v>2648</v>
+      </c>
+      <c r="AB608">
+        <v>1459</v>
+      </c>
+      <c r="AC608">
+        <v>10002</v>
+      </c>
+      <c r="AD608">
+        <v>4922</v>
+      </c>
+      <c r="AE608">
+        <v>10005</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="639">
   <si>
     <t>date</t>
   </si>
@@ -1928,6 +1928,9 @@
   </si>
   <si>
     <t>2026-10-29</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
   </si>
 </sst>
 </file>
@@ -2270,7 +2273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE608"/>
+  <dimension ref="A1:AE609"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -59772,6 +59775,101 @@
         <v>10005</v>
       </c>
     </row>
+    <row r="609" spans="1:31">
+      <c r="A609" t="s">
+        <v>638</v>
+      </c>
+      <c r="B609">
+        <v>447</v>
+      </c>
+      <c r="C609">
+        <v>1779</v>
+      </c>
+      <c r="D609">
+        <v>10026</v>
+      </c>
+      <c r="E609">
+        <v>1666</v>
+      </c>
+      <c r="F609">
+        <v>4459</v>
+      </c>
+      <c r="G609">
+        <v>5452</v>
+      </c>
+      <c r="H609">
+        <v>160</v>
+      </c>
+      <c r="I609">
+        <v>10021</v>
+      </c>
+      <c r="J609">
+        <v>7394</v>
+      </c>
+      <c r="K609">
+        <v>3114</v>
+      </c>
+      <c r="L609">
+        <v>884</v>
+      </c>
+      <c r="M609">
+        <v>1269</v>
+      </c>
+      <c r="N609">
+        <v>0</v>
+      </c>
+      <c r="O609">
+        <v>0</v>
+      </c>
+      <c r="P609">
+        <v>2745</v>
+      </c>
+      <c r="Q609">
+        <v>4356</v>
+      </c>
+      <c r="R609">
+        <v>243</v>
+      </c>
+      <c r="S609">
+        <v>2325</v>
+      </c>
+      <c r="T609">
+        <v>250</v>
+      </c>
+      <c r="U609">
+        <v>0</v>
+      </c>
+      <c r="V609">
+        <v>147</v>
+      </c>
+      <c r="W609">
+        <v>947</v>
+      </c>
+      <c r="X609">
+        <v>1316</v>
+      </c>
+      <c r="Y609">
+        <v>57</v>
+      </c>
+      <c r="Z609">
+        <v>265</v>
+      </c>
+      <c r="AA609">
+        <v>2648</v>
+      </c>
+      <c r="AB609">
+        <v>1459</v>
+      </c>
+      <c r="AC609">
+        <v>10000</v>
+      </c>
+      <c r="AD609">
+        <v>4920</v>
+      </c>
+      <c r="AE609">
+        <v>10002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bsky_followers.xlsx
+++ b/bsky_followers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="640">
   <si>
     <t>date</t>
   </si>
@@ -1931,6 +1931,9 @@
   </si>
   <si>
     <t>2026-10-30</t>
+  </si>
+  <si>
+    <t>2026-10-31</t>
   </si>
 </sst>
 </file>
@@ -2273,7 +2276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE609"/>
+  <dimension ref="A1:AE610"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1">
@@ -59870,6 +59873,101 @@
         <v>10002</v>
       </c>
     </row>
+    <row r="610" spans="1:31">
+      <c r="A610" t="s">
+        <v>639</v>
+      </c>
+      <c r="B610">
+        <v>447</v>
+      </c>
+      <c r="C610">
+        <v>1781</v>
+      </c>
+      <c r="D610">
+        <v>10067</v>
+      </c>
+      <c r="E610">
+        <v>1666</v>
+      </c>
+      <c r="F610">
+        <v>4460</v>
+      </c>
+      <c r="G610">
+        <v>5451</v>
+      </c>
+      <c r="H610">
+        <v>160</v>
+      </c>
+      <c r="I610">
+        <v>10019</v>
+      </c>
+      <c r="J610">
+        <v>7394</v>
+      </c>
+      <c r="K610">
+        <v>3114</v>
+      </c>
+      <c r="L610">
+        <v>883</v>
+      </c>
+      <c r="M610">
+        <v>1270</v>
+      </c>
+      <c r="N610">
+        <v>0</v>
+      </c>
+      <c r="O610">
+        <v>0</v>
+      </c>
+      <c r="P610">
+        <v>2746</v>
+      </c>
+      <c r="Q610">
+        <v>4357</v>
+      </c>
+      <c r="R610">
+        <v>243</v>
+      </c>
+      <c r="S610">
+        <v>2326</v>
+      </c>
+      <c r="T610">
+        <v>250</v>
+      </c>
+      <c r="U610">
+        <v>0</v>
+      </c>
+      <c r="V610">
+        <v>147</v>
+      </c>
+      <c r="W610">
+        <v>947</v>
+      </c>
+      <c r="X610">
+        <v>1316</v>
+      </c>
+      <c r="Y610">
+        <v>57</v>
+      </c>
+      <c r="Z610">
+        <v>265</v>
+      </c>
+      <c r="AA610">
+        <v>2649</v>
+      </c>
+      <c r="AB610">
+        <v>1459</v>
+      </c>
+      <c r="AC610">
+        <v>10093</v>
+      </c>
+      <c r="AD610">
+        <v>4922</v>
+      </c>
+      <c r="AE610">
+        <v>10002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
